--- a/experiment/HAT+CNN_2CH_bestx4/Collect/HAT_Collect.xlsx
+++ b/experiment/HAT+CNN_2CH_bestx4/Collect/HAT_Collect.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gama\Desktop\New folder\HAT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mohamed\Desktop\New folder\HAT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADAEEDE1-29AC-45DE-83A4-B80F5535B784}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FE8E0FB-E488-48E0-B19F-B0C5B4589E1F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PSNR" sheetId="1" r:id="rId1"/>
@@ -33,9 +33,6 @@
     <t>DHTCUN</t>
   </si>
   <si>
-    <t>HAT +CNN</t>
-  </si>
-  <si>
     <t>HAT_2CH</t>
   </si>
   <si>
@@ -43,6 +40,9 @@
   </si>
   <si>
     <t>HAT+CNN_2CH</t>
+  </si>
+  <si>
+    <t>HAT+CNN</t>
   </si>
 </sst>
 </file>
@@ -53,14 +53,14 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="4">
@@ -110,7 +110,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="12">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -119,7 +131,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="عادي" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -397,114 +409,114 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F407"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F411"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2">
         <v>28.780999999999999</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="1">
         <v>28.905000000000001</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="6">
         <v>28.172999999999998</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="1">
         <v>28.684000000000001</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="10">
         <v>28.512</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="1">
         <v>29.039000000000001</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="1">
         <v>29.428000000000001</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="6">
         <v>29.728000000000002</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="1">
         <v>29.004000000000001</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="10">
         <v>29.620999999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>2</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="1">
         <v>29.233000000000001</v>
       </c>
       <c r="C4">
         <v>29.36</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="6">
         <v>30.152999999999999</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="1">
         <v>30.137</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="10">
         <v>30.19</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>3</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="1">
         <v>28.885000000000002</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="1">
         <v>30.594999999999999</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="4">
         <v>30.053999999999998</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="1">
         <v>30.215</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="10">
         <v>30.332999999999998</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>4</v>
       </c>
@@ -514,437 +526,437 @@
       <c r="C6">
         <v>30.184999999999999</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="6">
         <v>30.212</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="1">
         <v>30.375</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="10">
         <v>30.914000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7">
         <v>29.427</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="1">
         <v>30.821000000000002</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="6">
         <v>30.937999999999999</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="1">
         <v>30.826000000000001</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="8">
         <v>30.675999999999998</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>6</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="1">
         <v>29.908000000000001</v>
       </c>
       <c r="C8">
         <v>30.658000000000001</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="4">
         <v>30.908000000000001</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="1">
         <v>31.09</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="8">
         <v>30.009</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>7</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="1">
         <v>30.199000000000002</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="1">
         <v>30.957000000000001</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="4">
         <v>30.056000000000001</v>
       </c>
       <c r="E9">
         <v>31.030999999999999</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="8">
         <v>30.812999999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>8</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="1">
         <v>30.399000000000001</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="1">
         <v>31.039000000000001</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="6">
         <v>31.033999999999999</v>
       </c>
       <c r="E10">
         <v>30.914999999999999</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="10">
         <v>31.056999999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>9</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="1">
         <v>30.567</v>
       </c>
       <c r="C11">
         <v>30.619</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="6">
         <v>31.259</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="1">
         <v>31.29</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="10">
         <v>31.123000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>10</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="1">
         <v>30.719000000000001</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="1">
         <v>31.088000000000001</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="6">
         <v>31.341999999999999</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="1">
         <v>31.324000000000002</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="8">
         <v>30.678999999999998</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>11</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="1">
         <v>30.838000000000001</v>
       </c>
       <c r="C13">
         <v>31.064</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="6">
         <v>31.388999999999999</v>
       </c>
       <c r="E13">
         <v>31.289000000000001</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="10">
         <v>31.234000000000002</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>12</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="1">
         <v>30.957000000000001</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="1">
         <v>31.378</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="6">
         <v>31.443999999999999</v>
       </c>
       <c r="E14">
         <v>31.073</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="10">
         <v>31.396000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>13</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="1">
         <v>31.067</v>
       </c>
       <c r="C15">
         <v>31.356000000000002</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="4">
         <v>31.414000000000001</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E15" s="1">
         <v>31.335999999999999</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="8">
         <v>31.388000000000002</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>14</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="1">
         <v>31.1</v>
       </c>
       <c r="C16">
         <v>31.039000000000001</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="6">
         <v>31.558</v>
       </c>
-      <c r="E16" s="2">
+      <c r="E16" s="1">
         <v>31.53</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="8">
         <v>31.251999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>15</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="1">
         <v>31.177</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="1">
         <v>31.465</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="6">
         <v>31.667999999999999</v>
       </c>
       <c r="E17">
         <v>31.422999999999998</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="10">
         <v>31.417999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>16</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18" s="1">
         <v>31.231999999999999</v>
       </c>
       <c r="C18">
         <v>31.34</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="4">
         <v>31.416</v>
       </c>
       <c r="E18">
         <v>31.48</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18" s="10">
         <v>31.565999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>17</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B19" s="1">
         <v>30.983000000000001</v>
       </c>
       <c r="C19">
         <v>31.324999999999999</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="4">
         <v>31.641999999999999</v>
       </c>
-      <c r="E19" s="2">
+      <c r="E19" s="1">
         <v>31.579000000000001</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="8">
         <v>31.236999999999998</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>18</v>
       </c>
       <c r="B20">
         <v>31.32</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C20" s="1">
         <v>31.538</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="4">
         <v>31.606999999999999</v>
       </c>
       <c r="E20">
         <v>31.57</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="8">
         <v>30.702000000000002</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>19</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B21" s="1">
         <v>31.324999999999999</v>
       </c>
       <c r="C21">
         <v>31.454999999999998</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="4">
         <v>31.661999999999999</v>
       </c>
       <c r="E21">
         <v>31.541</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F21" s="10">
         <v>31.701000000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>20</v>
       </c>
-      <c r="B22" s="2">
+      <c r="B22" s="1">
         <v>30.617999999999999</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C22" s="1">
         <v>31.626999999999999</v>
       </c>
-      <c r="D22" s="2">
+      <c r="D22" s="6">
         <v>31.702999999999999</v>
       </c>
-      <c r="E22" s="2">
+      <c r="E22" s="1">
         <v>31.748999999999999</v>
       </c>
-      <c r="F22" s="2">
+      <c r="F22" s="10">
         <v>31.773</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>21</v>
       </c>
       <c r="B23">
         <v>31.295999999999999</v>
       </c>
-      <c r="C23" s="2">
+      <c r="C23" s="1">
         <v>31.745999999999999</v>
       </c>
-      <c r="D23" s="2">
+      <c r="D23" s="6">
         <v>31.795999999999999</v>
       </c>
       <c r="E23">
         <v>31.695</v>
       </c>
-      <c r="F23">
+      <c r="F23" s="8">
         <v>31.677</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>22</v>
       </c>
       <c r="B24">
         <v>31.433</v>
       </c>
-      <c r="C24" s="2">
+      <c r="C24" s="1">
         <v>31.760999999999999</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="4">
         <v>31.477</v>
       </c>
       <c r="E24">
         <v>31.695</v>
       </c>
-      <c r="F24">
+      <c r="F24" s="8">
         <v>31.568999999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>23</v>
       </c>
-      <c r="B25" s="2">
+      <c r="B25" s="1">
         <v>31.501999999999999</v>
       </c>
       <c r="C25">
         <v>31.466999999999999</v>
       </c>
-      <c r="D25" s="2">
+      <c r="D25" s="6">
         <v>31.832999999999998</v>
       </c>
-      <c r="E25" s="2">
+      <c r="E25" s="1">
         <v>31.864999999999998</v>
       </c>
-      <c r="F25">
+      <c r="F25" s="8">
         <v>31.728999999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>24</v>
       </c>
-      <c r="B26" s="2">
+      <c r="B26" s="1">
         <v>31.574000000000002</v>
       </c>
-      <c r="C26" s="2">
+      <c r="C26" s="1">
         <v>31.792000000000002</v>
       </c>
-      <c r="D26" s="2">
+      <c r="D26" s="6">
         <v>31.838999999999999</v>
       </c>
       <c r="E26">
         <v>31.789000000000001</v>
       </c>
-      <c r="F26" s="2">
+      <c r="F26" s="10">
         <v>31.811</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>25</v>
       </c>
-      <c r="B27" s="2">
+      <c r="B27" s="1">
         <v>31.399000000000001</v>
       </c>
       <c r="C27">
         <v>31.515000000000001</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="4">
         <v>31.731000000000002</v>
       </c>
-      <c r="E27" s="2">
+      <c r="E27" s="1">
         <v>31.875</v>
       </c>
-      <c r="F27">
+      <c r="F27" s="8">
         <v>31.765999999999998</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>26</v>
       </c>
@@ -954,17 +966,17 @@
       <c r="C28">
         <v>31.605</v>
       </c>
-      <c r="D28" s="2">
+      <c r="D28" s="6">
         <v>31.904</v>
       </c>
       <c r="E28">
         <v>31.850999999999999</v>
       </c>
-      <c r="F28">
+      <c r="F28" s="8">
         <v>31.786999999999999</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>27</v>
       </c>
@@ -974,17 +986,17 @@
       <c r="C29">
         <v>31.74</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="4">
         <v>31.75</v>
       </c>
       <c r="E29">
         <v>31.302</v>
       </c>
-      <c r="F29" s="2">
+      <c r="F29" s="10">
         <v>31.895</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>28</v>
       </c>
@@ -994,17 +1006,17 @@
       <c r="C30">
         <v>31.54</v>
       </c>
-      <c r="D30" s="2">
+      <c r="D30" s="6">
         <v>31.916</v>
       </c>
       <c r="E30">
         <v>31.134</v>
       </c>
-      <c r="F30">
+      <c r="F30" s="8">
         <v>31.849</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>29</v>
       </c>
@@ -1014,77 +1026,77 @@
       <c r="C31">
         <v>31.78</v>
       </c>
-      <c r="D31">
+      <c r="D31" s="4">
         <v>31.902999999999999</v>
       </c>
-      <c r="E31" s="2">
+      <c r="E31" s="1">
         <v>31.946000000000002</v>
       </c>
-      <c r="F31">
+      <c r="F31" s="8">
         <v>31.826000000000001</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>30</v>
       </c>
-      <c r="B32" s="2">
+      <c r="B32" s="1">
         <v>31.780999999999999</v>
       </c>
-      <c r="C32" s="2">
+      <c r="C32" s="1">
         <v>31.856000000000002</v>
       </c>
-      <c r="D32" s="2">
+      <c r="D32" s="6">
         <v>31.917000000000002</v>
       </c>
-      <c r="E32" s="2">
+      <c r="E32" s="1">
         <v>31.960999999999999</v>
       </c>
-      <c r="F32">
+      <c r="F32" s="8">
         <v>31.678999999999998</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>31</v>
       </c>
-      <c r="B33" s="2">
+      <c r="B33" s="1">
         <v>31.795000000000002</v>
       </c>
       <c r="C33">
         <v>31.738</v>
       </c>
-      <c r="D33">
+      <c r="D33" s="4">
         <v>31.873999999999999</v>
       </c>
       <c r="E33">
         <v>31.922000000000001</v>
       </c>
-      <c r="F33" s="2">
+      <c r="F33" s="10">
         <v>31.971</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>32</v>
       </c>
-      <c r="B34" s="2">
+      <c r="B34" s="1">
         <v>31.783000000000001</v>
       </c>
-      <c r="C34" s="2">
+      <c r="C34" s="1">
         <v>31.911000000000001</v>
       </c>
-      <c r="D34">
+      <c r="D34" s="4">
         <v>31.8</v>
       </c>
       <c r="E34">
         <v>31.902999999999999</v>
       </c>
-      <c r="F34">
+      <c r="F34" s="8">
         <v>31.87</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>33</v>
       </c>
@@ -1094,57 +1106,57 @@
       <c r="C35">
         <v>31.898</v>
       </c>
-      <c r="D35">
+      <c r="D35" s="4">
         <v>31.753</v>
       </c>
       <c r="E35">
         <v>31.757999999999999</v>
       </c>
-      <c r="F35">
+      <c r="F35" s="8">
         <v>31.408000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>34</v>
       </c>
-      <c r="B36" s="2">
+      <c r="B36" s="1">
         <v>31.849</v>
       </c>
       <c r="C36">
         <v>31.867000000000001</v>
       </c>
-      <c r="D36" s="2">
+      <c r="D36" s="6">
         <v>32.03</v>
       </c>
-      <c r="E36" s="2">
+      <c r="E36" s="1">
         <v>31.977</v>
       </c>
-      <c r="F36">
+      <c r="F36" s="8">
         <v>31.927</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>35</v>
       </c>
-      <c r="B37" s="2">
+      <c r="B37" s="1">
         <v>31.483000000000001</v>
       </c>
-      <c r="C37" s="2">
+      <c r="C37" s="1">
         <v>31.986000000000001</v>
       </c>
-      <c r="D37">
+      <c r="D37" s="4">
         <v>31.841000000000001</v>
       </c>
       <c r="E37">
         <v>31.940999999999999</v>
       </c>
-      <c r="F37">
+      <c r="F37" s="8">
         <v>31.672000000000001</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>36</v>
       </c>
@@ -1154,17 +1166,17 @@
       <c r="C38">
         <v>31.954999999999998</v>
       </c>
-      <c r="D38">
+      <c r="D38" s="4">
         <v>31.236999999999998</v>
       </c>
-      <c r="E38" s="2">
+      <c r="E38" s="1">
         <v>32.029000000000003</v>
       </c>
-      <c r="F38">
+      <c r="F38" s="8">
         <v>31.908000000000001</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>37</v>
       </c>
@@ -1174,17 +1186,17 @@
       <c r="C39">
         <v>31.936</v>
       </c>
-      <c r="D39">
+      <c r="D39" s="4">
         <v>31.99</v>
       </c>
       <c r="E39">
         <v>32.026000000000003</v>
       </c>
-      <c r="F39">
+      <c r="F39" s="8">
         <v>31.949000000000002</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>38</v>
       </c>
@@ -1194,37 +1206,37 @@
       <c r="C40">
         <v>31.838000000000001</v>
       </c>
-      <c r="D40" s="2">
+      <c r="D40" s="6">
         <v>32.037999999999997</v>
       </c>
       <c r="E40">
         <v>31.745000000000001</v>
       </c>
-      <c r="F40">
+      <c r="F40" s="8">
         <v>31.876999999999999</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>39</v>
       </c>
-      <c r="B41" s="2">
+      <c r="B41" s="1">
         <v>31.632999999999999</v>
       </c>
       <c r="C41">
         <v>31.768999999999998</v>
       </c>
-      <c r="D41">
+      <c r="D41" s="4">
         <v>31.922999999999998</v>
       </c>
       <c r="E41">
         <v>31.99</v>
       </c>
-      <c r="F41">
+      <c r="F41" s="8">
         <v>31.853000000000002</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>40</v>
       </c>
@@ -1234,57 +1246,57 @@
       <c r="C42">
         <v>31.923999999999999</v>
       </c>
-      <c r="D42" s="2">
+      <c r="D42" s="6">
         <v>32.088000000000001</v>
       </c>
       <c r="E42">
         <v>31.728999999999999</v>
       </c>
-      <c r="F42">
+      <c r="F42" s="8">
         <v>31.885000000000002</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>41</v>
       </c>
-      <c r="B43" s="2">
+      <c r="B43" s="1">
         <v>31.946000000000002</v>
       </c>
       <c r="C43">
         <v>31.925000000000001</v>
       </c>
-      <c r="D43">
+      <c r="D43" s="4">
         <v>31.984999999999999</v>
       </c>
       <c r="E43">
         <v>31.914000000000001</v>
       </c>
-      <c r="F43">
+      <c r="F43" s="8">
         <v>31.922000000000001</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>42</v>
       </c>
-      <c r="B44" s="2">
+      <c r="B44" s="1">
         <v>31.776</v>
       </c>
       <c r="C44">
         <v>31.78</v>
       </c>
-      <c r="D44">
+      <c r="D44" s="4">
         <v>32.01</v>
       </c>
-      <c r="E44" s="2">
+      <c r="E44" s="1">
         <v>32.042999999999999</v>
       </c>
-      <c r="F44" s="2">
+      <c r="F44" s="10">
         <v>31.998000000000001</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>43</v>
       </c>
@@ -1294,17 +1306,17 @@
       <c r="C45">
         <v>31.946000000000002</v>
       </c>
-      <c r="D45">
+      <c r="D45" s="4">
         <v>31.946999999999999</v>
       </c>
-      <c r="E45" s="2">
+      <c r="E45" s="1">
         <v>32.109000000000002</v>
       </c>
-      <c r="F45" s="2">
+      <c r="F45" s="10">
         <v>32.020000000000003</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>44</v>
       </c>
@@ -1314,37 +1326,37 @@
       <c r="C46">
         <v>31.605</v>
       </c>
-      <c r="D46">
+      <c r="D46" s="4">
         <v>31.609000000000002</v>
       </c>
       <c r="E46">
         <v>32.088999999999999</v>
       </c>
-      <c r="F46">
+      <c r="F46" s="8">
         <v>31.945</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>45</v>
       </c>
       <c r="B47">
         <v>31.94</v>
       </c>
-      <c r="C47" s="2">
+      <c r="C47" s="1">
         <v>31.986999999999998</v>
       </c>
-      <c r="D47">
+      <c r="D47" s="4">
         <v>32.045999999999999</v>
       </c>
       <c r="E47">
         <v>31.777000000000001</v>
       </c>
-      <c r="F47" s="2">
+      <c r="F47" s="10">
         <v>32.067999999999998</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>46</v>
       </c>
@@ -1354,37 +1366,37 @@
       <c r="C48">
         <v>31.32</v>
       </c>
-      <c r="D48">
+      <c r="D48" s="4">
         <v>31.396000000000001</v>
       </c>
       <c r="E48">
         <v>31.934999999999999</v>
       </c>
-      <c r="F48">
+      <c r="F48" s="8">
         <v>32.008000000000003</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>47</v>
       </c>
-      <c r="B49" s="2">
+      <c r="B49" s="1">
         <v>31.881</v>
       </c>
       <c r="C49">
         <v>31.811</v>
       </c>
-      <c r="D49">
+      <c r="D49" s="4">
         <v>32.018999999999998</v>
       </c>
       <c r="E49">
         <v>32.058</v>
       </c>
-      <c r="F49">
+      <c r="F49" s="8">
         <v>31.864999999999998</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>48</v>
       </c>
@@ -1394,37 +1406,37 @@
       <c r="C50">
         <v>31.713000000000001</v>
       </c>
-      <c r="D50" s="2">
+      <c r="D50" s="6">
         <v>32.125</v>
       </c>
       <c r="E50">
         <v>31.753</v>
       </c>
-      <c r="F50" s="2">
+      <c r="F50" s="10">
         <v>32.082000000000001</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>49</v>
       </c>
-      <c r="B51" s="2">
+      <c r="B51" s="1">
         <v>31.981999999999999</v>
       </c>
-      <c r="C51" s="2">
+      <c r="C51" s="1">
         <v>32.036000000000001</v>
       </c>
-      <c r="D51" s="2">
+      <c r="D51" s="6">
         <v>32.142000000000003</v>
       </c>
       <c r="E51">
         <v>32.073</v>
       </c>
-      <c r="F51">
+      <c r="F51" s="8">
         <v>32.067999999999998</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>50</v>
       </c>
@@ -1434,37 +1446,37 @@
       <c r="C52">
         <v>31.846</v>
       </c>
-      <c r="D52">
+      <c r="D52" s="4">
         <v>32.139000000000003</v>
       </c>
       <c r="E52">
         <v>32</v>
       </c>
-      <c r="F52">
+      <c r="F52" s="8">
         <v>32.073999999999998</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>51</v>
       </c>
       <c r="B53">
         <v>31.99</v>
       </c>
-      <c r="C53" s="2">
+      <c r="C53" s="1">
         <v>32.061</v>
       </c>
-      <c r="D53">
+      <c r="D53" s="4">
         <v>31.949000000000002</v>
       </c>
       <c r="E53">
         <v>32.061</v>
       </c>
-      <c r="F53" s="2">
+      <c r="F53" s="10">
         <v>32.122</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>52</v>
       </c>
@@ -1474,17 +1486,17 @@
       <c r="C54">
         <v>31.422000000000001</v>
       </c>
-      <c r="D54" s="2">
+      <c r="D54" s="6">
         <v>32.167000000000002</v>
       </c>
       <c r="E54">
         <v>32.067</v>
       </c>
-      <c r="F54">
+      <c r="F54" s="8">
         <v>31.951000000000001</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>53</v>
       </c>
@@ -1494,77 +1506,77 @@
       <c r="C55">
         <v>31.968</v>
       </c>
-      <c r="D55">
+      <c r="D55" s="4">
         <v>32.154000000000003</v>
       </c>
-      <c r="E55" s="2">
+      <c r="E55" s="1">
         <v>32.176000000000002</v>
       </c>
-      <c r="F55" s="2">
+      <c r="F55" s="10">
         <v>32.143000000000001</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>54</v>
       </c>
-      <c r="B56" s="2">
+      <c r="B56" s="1">
         <v>32.098999999999997</v>
       </c>
       <c r="C56">
         <v>31.934999999999999</v>
       </c>
-      <c r="D56">
+      <c r="D56" s="4">
         <v>32.140999999999998</v>
       </c>
       <c r="E56">
         <v>32.091000000000001</v>
       </c>
-      <c r="F56">
+      <c r="F56" s="8">
         <v>32.081000000000003</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>55</v>
       </c>
-      <c r="B57" s="2">
+      <c r="B57" s="1">
         <v>31.969000000000001</v>
       </c>
       <c r="C57">
         <v>32.052999999999997</v>
       </c>
-      <c r="D57">
+      <c r="D57" s="4">
         <v>32.149000000000001</v>
       </c>
       <c r="E57">
         <v>32.137</v>
       </c>
-      <c r="F57" s="2">
+      <c r="F57" s="10">
         <v>32.158999999999999</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>56</v>
       </c>
       <c r="B58">
         <v>31.919</v>
       </c>
-      <c r="C58" s="2">
+      <c r="C58" s="1">
         <v>32.066000000000003</v>
       </c>
-      <c r="D58">
+      <c r="D58" s="4">
         <v>32.158000000000001</v>
       </c>
       <c r="E58">
         <v>32.06</v>
       </c>
-      <c r="F58" s="2">
+      <c r="F58" s="10">
         <v>32.162999999999997</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>57</v>
       </c>
@@ -1574,57 +1586,57 @@
       <c r="C59">
         <v>32.055999999999997</v>
       </c>
-      <c r="D59" s="2">
+      <c r="D59" s="6">
         <v>32.18</v>
       </c>
       <c r="E59">
         <v>31.791</v>
       </c>
-      <c r="F59">
+      <c r="F59" s="8">
         <v>31.974</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>58</v>
       </c>
-      <c r="B60" s="2">
+      <c r="B60" s="1">
         <v>32.136000000000003</v>
       </c>
       <c r="C60">
         <v>32.061999999999998</v>
       </c>
-      <c r="D60" s="2">
+      <c r="D60" s="6">
         <v>32.19</v>
       </c>
       <c r="E60">
         <v>32.140999999999998</v>
       </c>
-      <c r="F60">
+      <c r="F60" s="8">
         <v>32.058999999999997</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>59</v>
       </c>
-      <c r="B61" s="2">
+      <c r="B61" s="1">
         <v>31.99</v>
       </c>
       <c r="C61">
         <v>32.023000000000003</v>
       </c>
-      <c r="D61" s="2">
+      <c r="D61" s="6">
         <v>32.201000000000001</v>
       </c>
       <c r="E61">
         <v>32.127000000000002</v>
       </c>
-      <c r="F61">
+      <c r="F61" s="8">
         <v>32.104999999999997</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>60</v>
       </c>
@@ -1634,57 +1646,57 @@
       <c r="C62">
         <v>32.055999999999997</v>
       </c>
-      <c r="D62">
+      <c r="D62" s="4">
         <v>32.145000000000003</v>
       </c>
       <c r="E62">
         <v>32.167999999999999</v>
       </c>
-      <c r="F62">
+      <c r="F62" s="8">
         <v>32.04</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>61</v>
       </c>
       <c r="B63">
         <v>32.158999999999999</v>
       </c>
-      <c r="C63" s="2">
+      <c r="C63" s="1">
         <v>32.079000000000001</v>
       </c>
-      <c r="D63">
+      <c r="D63" s="4">
         <v>32.017000000000003</v>
       </c>
       <c r="E63">
         <v>32.151000000000003</v>
       </c>
-      <c r="F63">
+      <c r="F63" s="8">
         <v>32.146000000000001</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>62</v>
       </c>
-      <c r="B64" s="2">
+      <c r="B64" s="1">
         <v>32.134</v>
       </c>
       <c r="C64">
         <v>32.026000000000003</v>
       </c>
-      <c r="D64">
+      <c r="D64" s="4">
         <v>31.658999999999999</v>
       </c>
-      <c r="E64" s="2">
+      <c r="E64" s="1">
         <v>32.192</v>
       </c>
-      <c r="F64">
+      <c r="F64" s="8">
         <v>32.125</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>63</v>
       </c>
@@ -1694,17 +1706,17 @@
       <c r="C65">
         <v>31.966000000000001</v>
       </c>
-      <c r="D65">
+      <c r="D65" s="4">
         <v>32.112000000000002</v>
       </c>
-      <c r="E65" s="2">
+      <c r="E65" s="1">
         <v>32.216999999999999</v>
       </c>
-      <c r="F65">
+      <c r="F65" s="8">
         <v>32.155999999999999</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>64</v>
       </c>
@@ -1714,37 +1726,37 @@
       <c r="C66">
         <v>31.989000000000001</v>
       </c>
-      <c r="D66">
+      <c r="D66" s="4">
         <v>32.033999999999999</v>
       </c>
       <c r="E66">
         <v>32.201999999999998</v>
       </c>
-      <c r="F66">
+      <c r="F66" s="8">
         <v>32.058</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>65</v>
       </c>
       <c r="B67">
         <v>32.075000000000003</v>
       </c>
-      <c r="C67" s="2">
+      <c r="C67" s="1">
         <v>32.136000000000003</v>
       </c>
-      <c r="D67">
+      <c r="D67" s="4">
         <v>32.186999999999998</v>
       </c>
-      <c r="E67" s="2">
+      <c r="E67" s="1">
         <v>32.231000000000002</v>
       </c>
-      <c r="F67">
+      <c r="F67" s="8">
         <v>32.069000000000003</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>66</v>
       </c>
@@ -1754,37 +1766,37 @@
       <c r="C68">
         <v>31.716999999999999</v>
       </c>
-      <c r="D68" s="2">
+      <c r="D68" s="6">
         <v>32.204000000000001</v>
       </c>
-      <c r="E68" s="2">
+      <c r="E68" s="1">
         <v>32.235999999999997</v>
       </c>
-      <c r="F68">
+      <c r="F68" s="8">
         <v>32.073</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>67</v>
       </c>
-      <c r="B69" s="2">
+      <c r="B69" s="1">
         <v>32.177</v>
       </c>
       <c r="C69">
         <v>32.098999999999997</v>
       </c>
-      <c r="D69" s="2">
+      <c r="D69" s="6">
         <v>32.284999999999997</v>
       </c>
       <c r="E69">
         <v>32.207999999999998</v>
       </c>
-      <c r="F69" s="2">
+      <c r="F69" s="10">
         <v>32.225000000000001</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>68</v>
       </c>
@@ -1794,37 +1806,37 @@
       <c r="C70">
         <v>31.984999999999999</v>
       </c>
-      <c r="D70">
+      <c r="D70" s="4">
         <v>32.011000000000003</v>
       </c>
       <c r="E70">
         <v>32.168999999999997</v>
       </c>
-      <c r="F70">
+      <c r="F70" s="8">
         <v>32.209000000000003</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>69</v>
       </c>
       <c r="B71">
         <v>32.174999999999997</v>
       </c>
-      <c r="C71" s="2">
+      <c r="C71" s="1">
         <v>32.155000000000001</v>
       </c>
-      <c r="D71">
+      <c r="D71" s="4">
         <v>32.228000000000002</v>
       </c>
       <c r="E71">
         <v>32.082000000000001</v>
       </c>
-      <c r="F71">
+      <c r="F71" s="8">
         <v>31.942</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>70</v>
       </c>
@@ -1834,17 +1846,17 @@
       <c r="C72">
         <v>32.018999999999998</v>
       </c>
-      <c r="D72">
+      <c r="D72" s="4">
         <v>32.018999999999998</v>
       </c>
-      <c r="E72" s="2">
+      <c r="E72" s="1">
         <v>32.262</v>
       </c>
-      <c r="F72">
+      <c r="F72" s="8">
         <v>32.045999999999999</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>71</v>
       </c>
@@ -1854,17 +1866,17 @@
       <c r="C73">
         <v>32.1</v>
       </c>
-      <c r="D73">
+      <c r="D73" s="4">
         <v>32.253999999999998</v>
       </c>
       <c r="E73">
         <v>32.19</v>
       </c>
-      <c r="F73">
+      <c r="F73" s="8">
         <v>32.200000000000003</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>72</v>
       </c>
@@ -1874,37 +1886,37 @@
       <c r="C74">
         <v>32.097000000000001</v>
       </c>
-      <c r="D74">
+      <c r="D74" s="4">
         <v>32.195999999999998</v>
       </c>
       <c r="E74">
         <v>32.21</v>
       </c>
-      <c r="F74">
+      <c r="F74" s="8">
         <v>31.998999999999999</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>73</v>
       </c>
-      <c r="B75" s="2">
+      <c r="B75" s="1">
         <v>32.131</v>
       </c>
       <c r="C75">
         <v>32.098999999999997</v>
       </c>
-      <c r="D75">
+      <c r="D75" s="4">
         <v>32.198999999999998</v>
       </c>
       <c r="E75">
         <v>32.220999999999997</v>
       </c>
-      <c r="F75">
+      <c r="F75" s="8">
         <v>32.04</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>74</v>
       </c>
@@ -1914,57 +1926,57 @@
       <c r="C76">
         <v>32.097999999999999</v>
       </c>
-      <c r="D76">
+      <c r="D76" s="4">
         <v>32.084000000000003</v>
       </c>
       <c r="E76">
         <v>32.051000000000002</v>
       </c>
-      <c r="F76">
+      <c r="F76" s="8">
         <v>31.858000000000001</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>75</v>
       </c>
-      <c r="B77" s="2">
+      <c r="B77" s="1">
         <v>32.264000000000003</v>
       </c>
       <c r="C77">
         <v>32.15</v>
       </c>
-      <c r="D77" s="2">
+      <c r="D77" s="6">
         <v>32.301000000000002</v>
       </c>
       <c r="E77">
         <v>32.076999999999998</v>
       </c>
-      <c r="F77">
+      <c r="F77" s="8">
         <v>32.173999999999999</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>76</v>
       </c>
-      <c r="B78" s="2">
+      <c r="B78" s="1">
         <v>32.073999999999998</v>
       </c>
       <c r="C78">
         <v>31.643000000000001</v>
       </c>
-      <c r="D78">
+      <c r="D78" s="4">
         <v>32.265000000000001</v>
       </c>
       <c r="E78">
         <v>32.234000000000002</v>
       </c>
-      <c r="F78">
+      <c r="F78" s="8">
         <v>32.097999999999999</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>77</v>
       </c>
@@ -1974,17 +1986,17 @@
       <c r="C79">
         <v>31.997</v>
       </c>
-      <c r="D79">
+      <c r="D79" s="4">
         <v>32.167999999999999</v>
       </c>
-      <c r="E79" s="2">
+      <c r="E79" s="1">
         <v>32.265000000000001</v>
       </c>
-      <c r="F79">
+      <c r="F79" s="8">
         <v>32.212000000000003</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>78</v>
       </c>
@@ -1994,37 +2006,37 @@
       <c r="C80">
         <v>31.995999999999999</v>
       </c>
-      <c r="D80">
+      <c r="D80" s="4">
         <v>32.277000000000001</v>
       </c>
       <c r="E80">
         <v>32.088000000000001</v>
       </c>
-      <c r="F80">
+      <c r="F80" s="8">
         <v>31.986999999999998</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>79</v>
       </c>
       <c r="B81">
         <v>32.159999999999997</v>
       </c>
-      <c r="C81" s="2">
+      <c r="C81" s="1">
         <v>32.180999999999997</v>
       </c>
-      <c r="D81">
+      <c r="D81" s="4">
         <v>32.218000000000004</v>
       </c>
-      <c r="E81" s="2">
+      <c r="E81" s="1">
         <v>32.302</v>
       </c>
-      <c r="F81">
+      <c r="F81" s="8">
         <v>32.19</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>80</v>
       </c>
@@ -2034,57 +2046,57 @@
       <c r="C82">
         <v>31.974</v>
       </c>
-      <c r="D82">
+      <c r="D82" s="4">
         <v>32.155999999999999</v>
       </c>
-      <c r="E82" s="2">
+      <c r="E82" s="1">
         <v>32.325000000000003</v>
       </c>
-      <c r="F82">
+      <c r="F82" s="8">
         <v>32.201000000000001</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>81</v>
       </c>
-      <c r="B83" s="2">
+      <c r="B83" s="1">
         <v>32.316000000000003</v>
       </c>
       <c r="C83">
         <v>31.869</v>
       </c>
-      <c r="D83">
+      <c r="D83" s="4">
         <v>32.042000000000002</v>
       </c>
       <c r="E83">
         <v>32.293999999999997</v>
       </c>
-      <c r="F83">
+      <c r="F83" s="8">
         <v>32.212000000000003</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>82</v>
       </c>
-      <c r="B84" s="2">
+      <c r="B84" s="1">
         <v>32.283000000000001</v>
       </c>
-      <c r="C84" s="2">
+      <c r="C84" s="1">
         <v>32.191000000000003</v>
       </c>
-      <c r="D84">
+      <c r="D84" s="4">
         <v>32.238</v>
       </c>
       <c r="E84">
         <v>32.313000000000002</v>
       </c>
-      <c r="F84" s="2">
+      <c r="F84" s="10">
         <v>32.280999999999999</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>83</v>
       </c>
@@ -2094,17 +2106,17 @@
       <c r="C85">
         <v>32.125</v>
       </c>
-      <c r="D85" s="2">
+      <c r="D85" s="6">
         <v>32.31</v>
       </c>
       <c r="E85">
         <v>32.276000000000003</v>
       </c>
-      <c r="F85">
+      <c r="F85" s="8">
         <v>32.262999999999998</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>84</v>
       </c>
@@ -2114,17 +2126,17 @@
       <c r="C86">
         <v>32.1</v>
       </c>
-      <c r="D86">
+      <c r="D86" s="4">
         <v>32.277999999999999</v>
       </c>
-      <c r="E86" s="2">
+      <c r="E86" s="1">
         <v>32.331000000000003</v>
       </c>
-      <c r="F86">
+      <c r="F86" s="8">
         <v>32.243000000000002</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>85</v>
       </c>
@@ -2134,17 +2146,17 @@
       <c r="C87">
         <v>32.097000000000001</v>
       </c>
-      <c r="D87">
+      <c r="D87" s="4">
         <v>32.29</v>
       </c>
       <c r="E87">
         <v>32.07</v>
       </c>
-      <c r="F87">
+      <c r="F87" s="8">
         <v>31.988</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>86</v>
       </c>
@@ -2154,77 +2166,77 @@
       <c r="C88">
         <v>32.164999999999999</v>
       </c>
-      <c r="D88" s="2">
+      <c r="D88" s="6">
         <v>32.326999999999998</v>
       </c>
       <c r="E88">
         <v>32.164999999999999</v>
       </c>
-      <c r="F88" s="2">
+      <c r="F88" s="10">
         <v>32.298999999999999</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>87</v>
       </c>
       <c r="B89">
         <v>32.267000000000003</v>
       </c>
-      <c r="C89" s="2">
+      <c r="C89" s="1">
         <v>32.207999999999998</v>
       </c>
-      <c r="D89">
+      <c r="D89" s="4">
         <v>32.302</v>
       </c>
       <c r="E89">
         <v>32.302999999999997</v>
       </c>
-      <c r="F89">
+      <c r="F89" s="8">
         <v>31.984999999999999</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>88</v>
       </c>
       <c r="B90">
         <v>32.337000000000003</v>
       </c>
-      <c r="C90" s="2">
+      <c r="C90" s="1">
         <v>32.24</v>
       </c>
-      <c r="D90">
+      <c r="D90" s="4">
         <v>32.119</v>
       </c>
       <c r="E90">
         <v>32.293999999999997</v>
       </c>
-      <c r="F90">
+      <c r="F90" s="8">
         <v>32.210999999999999</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>89</v>
       </c>
-      <c r="B91" s="2">
+      <c r="B91" s="1">
         <v>32.250999999999998</v>
       </c>
       <c r="C91">
         <v>32.162999999999997</v>
       </c>
-      <c r="D91">
+      <c r="D91" s="4">
         <v>32.253999999999998</v>
       </c>
-      <c r="E91" s="2">
+      <c r="E91" s="1">
         <v>32.340000000000003</v>
       </c>
-      <c r="F91">
+      <c r="F91" s="8">
         <v>32.21</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>90</v>
       </c>
@@ -2234,17 +2246,17 @@
       <c r="C92">
         <v>32.222000000000001</v>
       </c>
-      <c r="D92">
+      <c r="D92" s="4">
         <v>32.289000000000001</v>
       </c>
       <c r="E92">
         <v>32.308999999999997</v>
       </c>
-      <c r="F92">
+      <c r="F92" s="8">
         <v>32.273000000000003</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>91</v>
       </c>
@@ -2254,17 +2266,17 @@
       <c r="C93">
         <v>32.191000000000003</v>
       </c>
-      <c r="D93" s="2">
+      <c r="D93" s="6">
         <v>32.328000000000003</v>
       </c>
       <c r="E93">
         <v>32.18</v>
       </c>
-      <c r="F93">
+      <c r="F93" s="8">
         <v>31.565999999999999</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>92</v>
       </c>
@@ -2274,37 +2286,37 @@
       <c r="C94">
         <v>32.14</v>
       </c>
-      <c r="D94">
+      <c r="D94" s="4">
         <v>32.085999999999999</v>
       </c>
       <c r="E94">
         <v>32.325000000000003</v>
       </c>
-      <c r="F94">
+      <c r="F94" s="8">
         <v>32.213999999999999</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>93</v>
       </c>
-      <c r="B95" s="2">
+      <c r="B95" s="1">
         <v>32.332000000000001</v>
       </c>
       <c r="C95">
         <v>32.109000000000002</v>
       </c>
-      <c r="D95">
+      <c r="D95" s="4">
         <v>32.265000000000001</v>
       </c>
-      <c r="E95" s="2">
+      <c r="E95" s="1">
         <v>32.353999999999999</v>
       </c>
-      <c r="F95" s="2">
+      <c r="F95" s="10">
         <v>32.325000000000003</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>94</v>
       </c>
@@ -2314,17 +2326,17 @@
       <c r="C96">
         <v>32.194000000000003</v>
       </c>
-      <c r="D96" s="2">
+      <c r="D96" s="6">
         <v>32.363</v>
       </c>
       <c r="E96">
         <v>32.33</v>
       </c>
-      <c r="F96">
+      <c r="F96" s="8">
         <v>32.316000000000003</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>95</v>
       </c>
@@ -2334,17 +2346,17 @@
       <c r="C97">
         <v>32.137</v>
       </c>
-      <c r="D97">
+      <c r="D97" s="4">
         <v>32.197000000000003</v>
       </c>
       <c r="E97">
         <v>32.335000000000001</v>
       </c>
-      <c r="F97">
+      <c r="F97" s="8">
         <v>32.14</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>96</v>
       </c>
@@ -2354,17 +2366,17 @@
       <c r="C98">
         <v>32.209000000000003</v>
       </c>
-      <c r="D98">
+      <c r="D98" s="4">
         <v>32.347000000000001</v>
       </c>
       <c r="E98">
         <v>32.341999999999999</v>
       </c>
-      <c r="F98">
+      <c r="F98" s="8">
         <v>32.256999999999998</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>97</v>
       </c>
@@ -2374,17 +2386,17 @@
       <c r="C99">
         <v>32.012999999999998</v>
       </c>
-      <c r="D99">
+      <c r="D99" s="4">
         <v>32.329000000000001</v>
       </c>
       <c r="E99">
         <v>32.292999999999999</v>
       </c>
-      <c r="F99">
+      <c r="F99" s="8">
         <v>32.270000000000003</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>98</v>
       </c>
@@ -2394,37 +2406,37 @@
       <c r="C100">
         <v>32.134999999999998</v>
       </c>
-      <c r="D100">
+      <c r="D100" s="4">
         <v>32.345999999999997</v>
       </c>
       <c r="E100">
         <v>32.341999999999999</v>
       </c>
-      <c r="F100">
+      <c r="F100" s="8">
         <v>32.255000000000003</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>99</v>
       </c>
-      <c r="B101" s="2">
+      <c r="B101" s="1">
         <v>32.381999999999998</v>
       </c>
       <c r="C101">
         <v>32.195</v>
       </c>
-      <c r="D101">
+      <c r="D101" s="4">
         <v>32.305</v>
       </c>
       <c r="E101">
         <v>32.338999999999999</v>
       </c>
-      <c r="F101">
+      <c r="F101" s="8">
         <v>32.31</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>100</v>
       </c>
@@ -2434,17 +2446,17 @@
       <c r="C102">
         <v>32.03</v>
       </c>
-      <c r="D102">
+      <c r="D102" s="4">
         <v>32.316000000000003</v>
       </c>
       <c r="E102">
         <v>32.32</v>
       </c>
-      <c r="F102" s="2">
+      <c r="F102" s="10">
         <v>32.326999999999998</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>101</v>
       </c>
@@ -2454,17 +2466,17 @@
       <c r="C103">
         <v>32.223999999999997</v>
       </c>
-      <c r="D103">
+      <c r="D103" s="4">
         <v>32.290999999999997</v>
       </c>
       <c r="E103">
         <v>32.286999999999999</v>
       </c>
-      <c r="F103">
+      <c r="F103" s="8">
         <v>32.317</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>102</v>
       </c>
@@ -2474,17 +2486,17 @@
       <c r="C104">
         <v>32.222000000000001</v>
       </c>
-      <c r="D104">
+      <c r="D104" s="4">
         <v>32.350999999999999</v>
       </c>
       <c r="E104">
         <v>32.302</v>
       </c>
-      <c r="F104">
+      <c r="F104" s="8">
         <v>32.319000000000003</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>103</v>
       </c>
@@ -2494,17 +2506,17 @@
       <c r="C105">
         <v>32.204999999999998</v>
       </c>
-      <c r="D105">
+      <c r="D105" s="4">
         <v>32.360999999999997</v>
       </c>
       <c r="E105">
         <v>32.308999999999997</v>
       </c>
-      <c r="F105" s="2">
+      <c r="F105" s="10">
         <v>32.356999999999999</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>104</v>
       </c>
@@ -2514,17 +2526,17 @@
       <c r="C106">
         <v>32.186</v>
       </c>
-      <c r="D106" s="2">
+      <c r="D106" s="6">
         <v>32.398000000000003</v>
       </c>
       <c r="E106">
         <v>32.311999999999998</v>
       </c>
-      <c r="F106">
+      <c r="F106" s="8">
         <v>32.323</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>105</v>
       </c>
@@ -2534,37 +2546,37 @@
       <c r="C107">
         <v>32.231000000000002</v>
       </c>
-      <c r="D107">
+      <c r="D107" s="4">
         <v>32.299999999999997</v>
       </c>
       <c r="E107">
         <v>32.29</v>
       </c>
-      <c r="F107">
+      <c r="F107" s="8">
         <v>32.268000000000001</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>106</v>
       </c>
       <c r="B108">
         <v>32.329000000000001</v>
       </c>
-      <c r="C108" s="2">
+      <c r="C108" s="1">
         <v>32.268999999999998</v>
       </c>
-      <c r="D108">
+      <c r="D108" s="4">
         <v>32.363</v>
       </c>
       <c r="E108">
         <v>32.320999999999998</v>
       </c>
-      <c r="F108">
+      <c r="F108" s="8">
         <v>32.225999999999999</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>107</v>
       </c>
@@ -2574,17 +2586,17 @@
       <c r="C109">
         <v>32.186</v>
       </c>
-      <c r="D109">
+      <c r="D109" s="4">
         <v>32.341000000000001</v>
       </c>
-      <c r="E109" s="2">
+      <c r="E109" s="1">
         <v>32.405999999999999</v>
       </c>
-      <c r="F109">
+      <c r="F109" s="8">
         <v>32.32</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>108</v>
       </c>
@@ -2594,17 +2606,17 @@
       <c r="C110">
         <v>32.247</v>
       </c>
-      <c r="D110">
+      <c r="D110" s="4">
         <v>32.287999999999997</v>
       </c>
       <c r="E110">
         <v>32.28</v>
       </c>
-      <c r="F110">
+      <c r="F110" s="8">
         <v>32.302</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>109</v>
       </c>
@@ -2614,17 +2626,17 @@
       <c r="C111">
         <v>32.255000000000003</v>
       </c>
-      <c r="D111">
+      <c r="D111" s="4">
         <v>31.974</v>
       </c>
       <c r="E111">
         <v>32.366</v>
       </c>
-      <c r="F111">
+      <c r="F111" s="8">
         <v>32.261000000000003</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>110</v>
       </c>
@@ -2634,37 +2646,37 @@
       <c r="C112">
         <v>32.259</v>
       </c>
-      <c r="D112" s="2">
+      <c r="D112" s="6">
         <v>32.411999999999999</v>
       </c>
       <c r="E112">
         <v>32.302</v>
       </c>
-      <c r="F112">
+      <c r="F112" s="8">
         <v>32.322000000000003</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>111</v>
       </c>
-      <c r="B113" s="2">
+      <c r="B113" s="1">
         <v>32.384999999999998</v>
       </c>
       <c r="C113">
         <v>32.256999999999998</v>
       </c>
-      <c r="D113" s="2">
+      <c r="D113" s="6">
         <v>32.415999999999997</v>
       </c>
       <c r="E113">
         <v>32.398000000000003</v>
       </c>
-      <c r="F113">
+      <c r="F113" s="8">
         <v>32.304000000000002</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A114">
         <v>112</v>
       </c>
@@ -2674,17 +2686,17 @@
       <c r="C114">
         <v>32.252000000000002</v>
       </c>
-      <c r="D114">
+      <c r="D114" s="4">
         <v>32.402000000000001</v>
       </c>
       <c r="E114">
         <v>32.386000000000003</v>
       </c>
-      <c r="F114" s="2">
+      <c r="F114" s="10">
         <v>32.359000000000002</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>113</v>
       </c>
@@ -2694,37 +2706,37 @@
       <c r="C115">
         <v>32.209000000000003</v>
       </c>
-      <c r="D115">
+      <c r="D115" s="4">
         <v>32.402000000000001</v>
       </c>
       <c r="E115">
         <v>32.371000000000002</v>
       </c>
-      <c r="F115">
+      <c r="F115" s="8">
         <v>32.271999999999998</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>114</v>
       </c>
       <c r="B116">
         <v>32.381999999999998</v>
       </c>
-      <c r="C116" s="2">
+      <c r="C116" s="1">
         <v>32.284999999999997</v>
       </c>
-      <c r="D116">
+      <c r="D116" s="4">
         <v>32.345999999999997</v>
       </c>
       <c r="E116">
         <v>32.354999999999997</v>
       </c>
-      <c r="F116" s="2">
+      <c r="F116" s="10">
         <v>32.360999999999997</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>115</v>
       </c>
@@ -2734,17 +2746,17 @@
       <c r="C117">
         <v>32.237000000000002</v>
       </c>
-      <c r="D117">
+      <c r="D117" s="4">
         <v>32.369999999999997</v>
       </c>
       <c r="E117">
         <v>32.372999999999998</v>
       </c>
-      <c r="F117">
+      <c r="F117" s="8">
         <v>32.335000000000001</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>116</v>
       </c>
@@ -2754,37 +2766,37 @@
       <c r="C118">
         <v>32.204000000000001</v>
       </c>
-      <c r="D118">
+      <c r="D118" s="4">
         <v>32.348999999999997</v>
       </c>
       <c r="E118">
         <v>32.372999999999998</v>
       </c>
-      <c r="F118">
+      <c r="F118" s="8">
         <v>32.338000000000001</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>117</v>
       </c>
       <c r="B119">
         <v>32.448999999999998</v>
       </c>
-      <c r="C119" s="2">
+      <c r="C119" s="1">
         <v>32.301000000000002</v>
       </c>
-      <c r="D119" s="2">
+      <c r="D119" s="6">
         <v>32.423000000000002</v>
       </c>
       <c r="E119">
         <v>32.390999999999998</v>
       </c>
-      <c r="F119" s="2">
+      <c r="F119" s="10">
         <v>32.377000000000002</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>118</v>
       </c>
@@ -2794,17 +2806,17 @@
       <c r="C120">
         <v>32.273000000000003</v>
       </c>
-      <c r="D120">
+      <c r="D120" s="4">
         <v>32.387999999999998</v>
       </c>
       <c r="E120">
         <v>32.348999999999997</v>
       </c>
-      <c r="F120">
+      <c r="F120" s="8">
         <v>32.29</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A121">
         <v>119</v>
       </c>
@@ -2814,17 +2826,17 @@
       <c r="C121">
         <v>32.25</v>
       </c>
-      <c r="D121">
+      <c r="D121" s="4">
         <v>32.335000000000001</v>
       </c>
       <c r="E121">
         <v>32.39</v>
       </c>
-      <c r="F121" s="2">
+      <c r="F121" s="10">
         <v>32.421999999999997</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A122">
         <v>120</v>
       </c>
@@ -2834,37 +2846,37 @@
       <c r="C122">
         <v>32.201999999999998</v>
       </c>
-      <c r="D122">
+      <c r="D122" s="4">
         <v>32.414999999999999</v>
       </c>
       <c r="E122">
         <v>32.384999999999998</v>
       </c>
-      <c r="F122">
+      <c r="F122" s="8">
         <v>32.369</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A123">
         <v>121</v>
       </c>
-      <c r="B123" s="2">
+      <c r="B123" s="1">
         <v>32.466999999999999</v>
       </c>
       <c r="C123">
         <v>32.277999999999999</v>
       </c>
-      <c r="D123">
+      <c r="D123" s="4">
         <v>32.345999999999997</v>
       </c>
       <c r="E123">
         <v>32.405000000000001</v>
       </c>
-      <c r="F123">
+      <c r="F123" s="8">
         <v>32.32</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A124">
         <v>122</v>
       </c>
@@ -2874,37 +2886,37 @@
       <c r="C124">
         <v>32.241</v>
       </c>
-      <c r="D124" s="2">
+      <c r="D124" s="6">
         <v>32.436</v>
       </c>
-      <c r="E124" s="2">
+      <c r="E124" s="1">
         <v>32.408999999999999</v>
       </c>
-      <c r="F124">
+      <c r="F124" s="8">
         <v>32.348999999999997</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A125">
         <v>123</v>
       </c>
-      <c r="B125" s="2">
+      <c r="B125" s="1">
         <v>32.319000000000003</v>
       </c>
       <c r="C125">
         <v>32.256</v>
       </c>
-      <c r="D125">
+      <c r="D125" s="4">
         <v>32.409999999999997</v>
       </c>
-      <c r="E125" s="2">
+      <c r="E125" s="1">
         <v>32.414000000000001</v>
       </c>
-      <c r="F125">
+      <c r="F125" s="8">
         <v>32.377000000000002</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A126">
         <v>124</v>
       </c>
@@ -2914,17 +2926,17 @@
       <c r="C126">
         <v>32.244</v>
       </c>
-      <c r="D126">
+      <c r="D126" s="4">
         <v>32.415999999999997</v>
       </c>
-      <c r="E126" s="2">
+      <c r="E126" s="1">
         <v>32.42</v>
       </c>
-      <c r="F126">
+      <c r="F126" s="8">
         <v>32.401000000000003</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A127">
         <v>125</v>
       </c>
@@ -2934,17 +2946,17 @@
       <c r="C127">
         <v>32.268999999999998</v>
       </c>
-      <c r="D127">
+      <c r="D127" s="4">
         <v>32.384999999999998</v>
       </c>
       <c r="E127">
         <v>32.341999999999999</v>
       </c>
-      <c r="F127">
+      <c r="F127" s="8">
         <v>32.305</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A128">
         <v>126</v>
       </c>
@@ -2954,17 +2966,17 @@
       <c r="C128">
         <v>32.286000000000001</v>
       </c>
-      <c r="D128">
+      <c r="D128" s="4">
         <v>32.381</v>
       </c>
       <c r="E128">
         <v>32.363</v>
       </c>
-      <c r="F128">
+      <c r="F128" s="8">
         <v>32.347000000000001</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A129">
         <v>127</v>
       </c>
@@ -2974,17 +2986,17 @@
       <c r="C129">
         <v>32.286000000000001</v>
       </c>
-      <c r="D129">
+      <c r="D129" s="4">
         <v>32.386000000000003</v>
       </c>
       <c r="E129">
         <v>32.417000000000002</v>
       </c>
-      <c r="F129">
+      <c r="F129" s="8">
         <v>32.341000000000001</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A130">
         <v>128</v>
       </c>
@@ -2994,17 +3006,17 @@
       <c r="C130">
         <v>32.276000000000003</v>
       </c>
-      <c r="D130">
+      <c r="D130" s="4">
         <v>32.418999999999997</v>
       </c>
       <c r="E130">
         <v>32.386000000000003</v>
       </c>
-      <c r="F130" s="2">
+      <c r="F130" s="10">
         <v>32.426000000000002</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A131">
         <v>129</v>
       </c>
@@ -3014,57 +3026,57 @@
       <c r="C131">
         <v>32.273000000000003</v>
       </c>
-      <c r="D131">
+      <c r="D131" s="4">
         <v>32.386000000000003</v>
       </c>
       <c r="E131">
         <v>32.337000000000003</v>
       </c>
-      <c r="F131">
+      <c r="F131" s="8">
         <v>32.369999999999997</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A132">
         <v>130</v>
       </c>
-      <c r="B132" s="2">
+      <c r="B132" s="1">
         <v>32.506</v>
       </c>
       <c r="C132">
         <v>32.264000000000003</v>
       </c>
-      <c r="D132">
+      <c r="D132" s="4">
         <v>32.399000000000001</v>
       </c>
       <c r="E132">
         <v>32.396000000000001</v>
       </c>
-      <c r="F132">
+      <c r="F132" s="8">
         <v>32.270000000000003</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A133">
         <v>131</v>
       </c>
-      <c r="B133" s="2">
+      <c r="B133" s="1">
         <v>32.423000000000002</v>
       </c>
-      <c r="C133" s="2">
+      <c r="C133" s="1">
         <v>32.313000000000002</v>
       </c>
-      <c r="D133">
+      <c r="D133" s="4">
         <v>32.420999999999999</v>
       </c>
       <c r="E133">
         <v>32.347000000000001</v>
       </c>
-      <c r="F133">
+      <c r="F133" s="8">
         <v>32.381</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A134">
         <v>132</v>
       </c>
@@ -3074,17 +3086,17 @@
       <c r="C134">
         <v>32.305999999999997</v>
       </c>
-      <c r="D134">
+      <c r="D134" s="4">
         <v>32.21</v>
       </c>
-      <c r="E134" s="2">
+      <c r="E134" s="1">
         <v>32.433999999999997</v>
       </c>
-      <c r="F134">
+      <c r="F134" s="8">
         <v>32.363</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A135">
         <v>133</v>
       </c>
@@ -3094,97 +3106,97 @@
       <c r="C135">
         <v>32.262999999999998</v>
       </c>
-      <c r="D135">
+      <c r="D135" s="4">
         <v>32.348999999999997</v>
       </c>
-      <c r="E135" s="2">
+      <c r="E135" s="1">
         <v>32.439</v>
       </c>
-      <c r="F135">
+      <c r="F135" s="8">
         <v>32.350999999999999</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A136">
         <v>134</v>
       </c>
-      <c r="B136" s="2">
+      <c r="B136" s="1">
         <v>32.548000000000002</v>
       </c>
-      <c r="C136" s="2">
+      <c r="C136" s="1">
         <v>32.317999999999998</v>
       </c>
-      <c r="D136">
+      <c r="D136" s="4">
         <v>32.387</v>
       </c>
-      <c r="E136" s="2">
+      <c r="E136" s="1">
         <v>32.451999999999998</v>
       </c>
-      <c r="F136">
+      <c r="F136" s="8">
         <v>32.354999999999997</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A137">
         <v>135</v>
       </c>
-      <c r="B137" s="2">
+      <c r="B137" s="1">
         <v>32.564999999999998</v>
       </c>
-      <c r="C137" s="2">
+      <c r="C137" s="1">
         <v>32.331000000000003</v>
       </c>
-      <c r="D137" s="2">
+      <c r="D137" s="6">
         <v>32.46</v>
       </c>
       <c r="E137">
         <v>32.380000000000003</v>
       </c>
-      <c r="F137">
+      <c r="F137" s="8">
         <v>32.402999999999999</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A138">
         <v>136</v>
       </c>
-      <c r="B138" s="2">
+      <c r="B138" s="1">
         <v>32.566000000000003</v>
       </c>
       <c r="C138">
         <v>32.31</v>
       </c>
-      <c r="D138">
+      <c r="D138" s="4">
         <v>32.456000000000003</v>
       </c>
       <c r="E138">
         <v>32.451000000000001</v>
       </c>
-      <c r="F138">
+      <c r="F138" s="8">
         <v>32.366999999999997</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A139">
         <v>137</v>
       </c>
-      <c r="B139" s="2">
+      <c r="B139" s="1">
         <v>32.554000000000002</v>
       </c>
-      <c r="C139" s="2">
+      <c r="C139" s="1">
         <v>32.353000000000002</v>
       </c>
-      <c r="D139">
+      <c r="D139" s="4">
         <v>32.433999999999997</v>
       </c>
       <c r="E139">
         <v>32.414999999999999</v>
       </c>
-      <c r="F139">
+      <c r="F139" s="8">
         <v>32.32</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A140">
         <v>138</v>
       </c>
@@ -3194,17 +3206,17 @@
       <c r="C140">
         <v>32.319000000000003</v>
       </c>
-      <c r="D140">
+      <c r="D140" s="4">
         <v>32.436999999999998</v>
       </c>
       <c r="E140">
         <v>32.427999999999997</v>
       </c>
-      <c r="F140" s="2">
+      <c r="F140" s="10">
         <v>32.436999999999998</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A141">
         <v>139</v>
       </c>
@@ -3214,37 +3226,37 @@
       <c r="C141">
         <v>32.270000000000003</v>
       </c>
-      <c r="D141">
+      <c r="D141" s="4">
         <v>32.408000000000001</v>
       </c>
       <c r="E141">
         <v>32.405999999999999</v>
       </c>
-      <c r="F141">
+      <c r="F141" s="8">
         <v>32.409999999999997</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A142">
         <v>140</v>
       </c>
       <c r="B142">
         <v>32.552</v>
       </c>
-      <c r="C142" s="2">
+      <c r="C142" s="1">
         <v>32.362000000000002</v>
       </c>
-      <c r="D142">
+      <c r="D142" s="4">
         <v>32.381</v>
       </c>
       <c r="E142">
         <v>32.427</v>
       </c>
-      <c r="F142">
+      <c r="F142" s="8">
         <v>32.402000000000001</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A143">
         <v>141</v>
       </c>
@@ -3254,17 +3266,17 @@
       <c r="C143">
         <v>32.326000000000001</v>
       </c>
-      <c r="D143">
+      <c r="D143" s="4">
         <v>32.414000000000001</v>
       </c>
       <c r="E143">
         <v>32.447000000000003</v>
       </c>
-      <c r="F143" s="2">
+      <c r="F143" s="10">
         <v>32.454000000000001</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A144">
         <v>142</v>
       </c>
@@ -3274,17 +3286,17 @@
       <c r="C144">
         <v>32.253</v>
       </c>
-      <c r="D144">
+      <c r="D144" s="4">
         <v>32.387</v>
       </c>
       <c r="E144">
         <v>32.451000000000001</v>
       </c>
-      <c r="F144">
+      <c r="F144" s="8">
         <v>32.393999999999998</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A145">
         <v>143</v>
       </c>
@@ -3294,17 +3306,17 @@
       <c r="C145">
         <v>32.298999999999999</v>
       </c>
-      <c r="D145">
+      <c r="D145" s="4">
         <v>32.393999999999998</v>
       </c>
       <c r="E145">
         <v>32.448</v>
       </c>
-      <c r="F145">
+      <c r="F145" s="8">
         <v>32.44</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A146">
         <v>144</v>
       </c>
@@ -3314,17 +3326,17 @@
       <c r="C146">
         <v>32.31</v>
       </c>
-      <c r="D146" s="2">
+      <c r="D146" s="6">
         <v>32.473999999999997</v>
       </c>
-      <c r="E146" s="2">
+      <c r="E146" s="1">
         <v>32.459000000000003</v>
       </c>
-      <c r="F146">
+      <c r="F146" s="8">
         <v>32.436999999999998</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A147">
         <v>145</v>
       </c>
@@ -3334,17 +3346,17 @@
       <c r="C147">
         <v>32.296999999999997</v>
       </c>
-      <c r="D147">
+      <c r="D147" s="4">
         <v>32.453000000000003</v>
       </c>
-      <c r="E147" s="2">
+      <c r="E147" s="1">
         <v>32.475000000000001</v>
       </c>
-      <c r="F147">
+      <c r="F147" s="8">
         <v>32.439</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A148">
         <v>146</v>
       </c>
@@ -3354,17 +3366,17 @@
       <c r="C148">
         <v>32.292999999999999</v>
       </c>
-      <c r="D148">
+      <c r="D148" s="4">
         <v>32.387</v>
       </c>
       <c r="E148">
         <v>32.447000000000003</v>
       </c>
-      <c r="F148" s="2">
+      <c r="F148" s="10">
         <v>32.46</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A149">
         <v>147</v>
       </c>
@@ -3374,17 +3386,17 @@
       <c r="C149">
         <v>32.350999999999999</v>
       </c>
-      <c r="D149">
+      <c r="D149" s="4">
         <v>32.454999999999998</v>
       </c>
       <c r="E149">
         <v>32.457000000000001</v>
       </c>
-      <c r="F149">
+      <c r="F149" s="8">
         <v>32.369999999999997</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A150">
         <v>148</v>
       </c>
@@ -3394,17 +3406,17 @@
       <c r="C150">
         <v>32.351999999999997</v>
       </c>
-      <c r="D150">
+      <c r="D150" s="4">
         <v>32.371000000000002</v>
       </c>
       <c r="E150">
         <v>32.445</v>
       </c>
-      <c r="F150" s="2">
+      <c r="F150" s="10">
         <v>32.463999999999999</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A151">
         <v>149</v>
       </c>
@@ -3414,17 +3426,17 @@
       <c r="C151">
         <v>32.36</v>
       </c>
-      <c r="D151">
+      <c r="D151" s="4">
         <v>32.454999999999998</v>
       </c>
       <c r="E151">
         <v>32.457999999999998</v>
       </c>
-      <c r="F151">
+      <c r="F151" s="8">
         <v>32.415999999999997</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A152">
         <v>150</v>
       </c>
@@ -3434,37 +3446,37 @@
       <c r="C152">
         <v>32.344000000000001</v>
       </c>
-      <c r="D152">
+      <c r="D152" s="4">
         <v>32.393000000000001</v>
       </c>
       <c r="E152">
         <v>32.447000000000003</v>
       </c>
-      <c r="F152" s="2">
+      <c r="F152" s="10">
         <v>32.475000000000001</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A153">
         <v>151</v>
       </c>
-      <c r="B153" s="2">
+      <c r="B153" s="1">
         <v>32.545000000000002</v>
       </c>
       <c r="C153">
         <v>32.335000000000001</v>
       </c>
-      <c r="D153" s="2">
+      <c r="D153" s="6">
         <v>32.488</v>
       </c>
       <c r="E153">
         <v>32.466000000000001</v>
       </c>
-      <c r="F153">
+      <c r="F153" s="8">
         <v>32.417000000000002</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A154">
         <v>152</v>
       </c>
@@ -3474,17 +3486,17 @@
       <c r="C154">
         <v>32.319000000000003</v>
       </c>
-      <c r="D154">
+      <c r="D154" s="4">
         <v>32.466999999999999</v>
       </c>
       <c r="E154">
         <v>32.46</v>
       </c>
-      <c r="F154" s="2">
+      <c r="F154" s="10">
         <v>32.494</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A155">
         <v>153</v>
       </c>
@@ -3494,17 +3506,17 @@
       <c r="C155">
         <v>32.316000000000003</v>
       </c>
-      <c r="D155">
+      <c r="D155" s="4">
         <v>32.424999999999997</v>
       </c>
       <c r="E155">
         <v>32.453000000000003</v>
       </c>
-      <c r="F155">
+      <c r="F155" s="8">
         <v>32.450000000000003</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A156">
         <v>154</v>
       </c>
@@ -3514,37 +3526,37 @@
       <c r="C156">
         <v>32.32</v>
       </c>
-      <c r="D156" s="2">
+      <c r="D156" s="6">
         <v>32.497</v>
       </c>
       <c r="E156">
         <v>32.447000000000003</v>
       </c>
-      <c r="F156" s="2">
+      <c r="F156" s="10">
         <v>32.502000000000002</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A157">
         <v>155</v>
       </c>
-      <c r="B157" s="2">
+      <c r="B157" s="1">
         <v>32.575000000000003</v>
       </c>
       <c r="C157">
         <v>32.329000000000001</v>
       </c>
-      <c r="D157">
+      <c r="D157" s="4">
         <v>32.466999999999999</v>
       </c>
       <c r="E157">
         <v>32.470999999999997</v>
       </c>
-      <c r="F157">
+      <c r="F157" s="8">
         <v>32.436999999999998</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A158">
         <v>156</v>
       </c>
@@ -3554,37 +3566,37 @@
       <c r="C158">
         <v>32.292000000000002</v>
       </c>
-      <c r="D158" s="2">
+      <c r="D158" s="6">
         <v>32.512999999999998</v>
       </c>
-      <c r="E158" s="2">
+      <c r="E158" s="1">
         <v>32.493000000000002</v>
       </c>
-      <c r="F158">
+      <c r="F158" s="8">
         <v>32.436999999999998</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A159">
         <v>157</v>
       </c>
-      <c r="B159" s="2">
+      <c r="B159" s="1">
         <v>32.582000000000001</v>
       </c>
       <c r="C159">
         <v>32.299999999999997</v>
       </c>
-      <c r="D159">
+      <c r="D159" s="4">
         <v>32.475000000000001</v>
       </c>
       <c r="E159">
         <v>32.469000000000001</v>
       </c>
-      <c r="F159">
+      <c r="F159" s="8">
         <v>32.465000000000003</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A160">
         <v>158</v>
       </c>
@@ -3594,37 +3606,37 @@
       <c r="C160">
         <v>32.173999999999999</v>
       </c>
-      <c r="D160">
+      <c r="D160" s="4">
         <v>32.459000000000003</v>
       </c>
       <c r="E160">
         <v>32.454000000000001</v>
       </c>
-      <c r="F160">
+      <c r="F160" s="8">
         <v>32.473999999999997</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A161">
         <v>159</v>
       </c>
-      <c r="B161" s="2">
+      <c r="B161" s="1">
         <v>32.581000000000003</v>
       </c>
       <c r="C161">
         <v>32.329000000000001</v>
       </c>
-      <c r="D161">
+      <c r="D161" s="4">
         <v>32.485999999999997</v>
       </c>
       <c r="E161">
         <v>32.487000000000002</v>
       </c>
-      <c r="F161">
+      <c r="F161" s="8">
         <v>32.442999999999998</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A162">
         <v>160</v>
       </c>
@@ -3634,57 +3646,57 @@
       <c r="C162">
         <v>32.353999999999999</v>
       </c>
-      <c r="D162">
+      <c r="D162" s="4">
         <v>32.457999999999998</v>
       </c>
       <c r="E162">
         <v>32.459000000000003</v>
       </c>
-      <c r="F162">
+      <c r="F162" s="8">
         <v>32.476999999999997</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A163">
         <v>161</v>
       </c>
       <c r="B163">
         <v>32.576999999999998</v>
       </c>
-      <c r="C163" s="2">
+      <c r="C163" s="1">
         <v>32.368000000000002</v>
       </c>
-      <c r="D163">
+      <c r="D163" s="4">
         <v>32.479999999999997</v>
       </c>
       <c r="E163">
         <v>32.450000000000003</v>
       </c>
-      <c r="F163">
+      <c r="F163" s="8">
         <v>32.49</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A164">
         <v>162</v>
       </c>
       <c r="B164">
         <v>32.585000000000001</v>
       </c>
-      <c r="C164" s="2">
+      <c r="C164" s="1">
         <v>32.378</v>
       </c>
-      <c r="D164">
+      <c r="D164" s="4">
         <v>32.511000000000003</v>
       </c>
       <c r="E164">
         <v>32.463000000000001</v>
       </c>
-      <c r="F164">
+      <c r="F164" s="8">
         <v>32.421999999999997</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A165">
         <v>163</v>
       </c>
@@ -3694,17 +3706,17 @@
       <c r="C165">
         <v>32.369999999999997</v>
       </c>
-      <c r="D165">
+      <c r="D165" s="4">
         <v>32.463999999999999</v>
       </c>
-      <c r="E165" s="2">
+      <c r="E165" s="1">
         <v>32.509</v>
       </c>
-      <c r="F165">
+      <c r="F165" s="8">
         <v>32.481000000000002</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A166">
         <v>164</v>
       </c>
@@ -3714,17 +3726,17 @@
       <c r="C166">
         <v>32.372</v>
       </c>
-      <c r="D166">
+      <c r="D166" s="4">
         <v>32.491999999999997</v>
       </c>
       <c r="E166">
         <v>32.472999999999999</v>
       </c>
-      <c r="F166">
+      <c r="F166" s="8">
         <v>32.295999999999999</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A167">
         <v>165</v>
       </c>
@@ -3734,17 +3746,17 @@
       <c r="C167">
         <v>32.305</v>
       </c>
-      <c r="D167" s="2">
+      <c r="D167" s="6">
         <v>32.517000000000003</v>
       </c>
       <c r="E167">
         <v>32.450000000000003</v>
       </c>
-      <c r="F167" s="2">
+      <c r="F167" s="10">
         <v>32.512</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A168">
         <v>166</v>
       </c>
@@ -3754,17 +3766,17 @@
       <c r="C168">
         <v>32.354999999999997</v>
       </c>
-      <c r="D168">
+      <c r="D168" s="4">
         <v>32.47</v>
       </c>
       <c r="E168">
         <v>32.49</v>
       </c>
-      <c r="F168">
+      <c r="F168" s="8">
         <v>32.473999999999997</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A169">
         <v>167</v>
       </c>
@@ -3774,37 +3786,37 @@
       <c r="C169">
         <v>32.348999999999997</v>
       </c>
-      <c r="D169">
+      <c r="D169" s="4">
         <v>32.506</v>
       </c>
       <c r="E169">
         <v>32.478999999999999</v>
       </c>
-      <c r="F169">
+      <c r="F169" s="8">
         <v>32.478999999999999</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A170">
         <v>168</v>
       </c>
-      <c r="B170" s="2">
+      <c r="B170" s="1">
         <v>32.561999999999998</v>
       </c>
       <c r="C170">
         <v>32.36</v>
       </c>
-      <c r="D170">
+      <c r="D170" s="4">
         <v>32.398000000000003</v>
       </c>
       <c r="E170">
         <v>32.5</v>
       </c>
-      <c r="F170">
+      <c r="F170" s="8">
         <v>32.488</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A171">
         <v>169</v>
       </c>
@@ -3814,17 +3826,17 @@
       <c r="C171">
         <v>32.279000000000003</v>
       </c>
-      <c r="D171">
+      <c r="D171" s="4">
         <v>32.506</v>
       </c>
       <c r="E171">
         <v>32.488</v>
       </c>
-      <c r="F171">
+      <c r="F171" s="8">
         <v>32.472999999999999</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A172">
         <v>170</v>
       </c>
@@ -3834,17 +3846,17 @@
       <c r="C172">
         <v>32.377000000000002</v>
       </c>
-      <c r="D172">
+      <c r="D172" s="4">
         <v>32.463999999999999</v>
       </c>
       <c r="E172">
         <v>32.499000000000002</v>
       </c>
-      <c r="F172" s="2">
+      <c r="F172" s="10">
         <v>32.523000000000003</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A173">
         <v>171</v>
       </c>
@@ -3854,37 +3866,37 @@
       <c r="C173">
         <v>32.372</v>
       </c>
-      <c r="D173">
+      <c r="D173" s="4">
         <v>32.468000000000004</v>
       </c>
       <c r="E173">
         <v>32.508000000000003</v>
       </c>
-      <c r="F173">
+      <c r="F173" s="8">
         <v>32.43</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A174">
         <v>172</v>
       </c>
       <c r="B174">
         <v>32.578000000000003</v>
       </c>
-      <c r="C174" s="2">
+      <c r="C174" s="1">
         <v>32.426000000000002</v>
       </c>
-      <c r="D174">
+      <c r="D174" s="4">
         <v>32.515000000000001</v>
       </c>
       <c r="E174">
         <v>32.493000000000002</v>
       </c>
-      <c r="F174">
+      <c r="F174" s="8">
         <v>32.484999999999999</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A175">
         <v>173</v>
       </c>
@@ -3894,17 +3906,17 @@
       <c r="C175">
         <v>32.417999999999999</v>
       </c>
-      <c r="D175">
+      <c r="D175" s="4">
         <v>32.447000000000003</v>
       </c>
       <c r="E175">
         <v>32.487000000000002</v>
       </c>
-      <c r="F175">
+      <c r="F175" s="8">
         <v>32.518999999999998</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A176">
         <v>174</v>
       </c>
@@ -3914,37 +3926,37 @@
       <c r="C176">
         <v>32.375</v>
       </c>
-      <c r="D176">
+      <c r="D176" s="4">
         <v>32.415999999999997</v>
       </c>
       <c r="E176">
         <v>32.496000000000002</v>
       </c>
-      <c r="F176">
+      <c r="F176" s="8">
         <v>32.505000000000003</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A177">
         <v>175</v>
       </c>
-      <c r="B177" s="2">
+      <c r="B177" s="1">
         <v>32.598999999999997</v>
       </c>
       <c r="C177">
         <v>32.396999999999998</v>
       </c>
-      <c r="D177">
+      <c r="D177" s="4">
         <v>32.493000000000002</v>
       </c>
       <c r="E177">
         <v>32.478000000000002</v>
       </c>
-      <c r="F177">
+      <c r="F177" s="8">
         <v>32.508000000000003</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A178">
         <v>176</v>
       </c>
@@ -3954,17 +3966,17 @@
       <c r="C178">
         <v>32.375</v>
       </c>
-      <c r="D178">
+      <c r="D178" s="4">
         <v>32.503</v>
       </c>
       <c r="E178">
         <v>32.494999999999997</v>
       </c>
-      <c r="F178">
+      <c r="F178" s="8">
         <v>32.499000000000002</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A179">
         <v>177</v>
       </c>
@@ -3974,17 +3986,17 @@
       <c r="C179">
         <v>32.405999999999999</v>
       </c>
-      <c r="D179">
+      <c r="D179" s="4">
         <v>32.515999999999998</v>
       </c>
       <c r="E179">
         <v>32.491999999999997</v>
       </c>
-      <c r="F179" s="2">
+      <c r="F179" s="10">
         <v>32.526000000000003</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A180">
         <v>178</v>
       </c>
@@ -3994,17 +4006,17 @@
       <c r="C180">
         <v>32.381</v>
       </c>
-      <c r="D180">
+      <c r="D180" s="4">
         <v>32.473999999999997</v>
       </c>
-      <c r="E180" s="2">
+      <c r="E180" s="1">
         <v>32.51</v>
       </c>
-      <c r="F180">
+      <c r="F180" s="8">
         <v>32.517000000000003</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A181">
         <v>179</v>
       </c>
@@ -4014,17 +4026,17 @@
       <c r="C181">
         <v>32.384</v>
       </c>
-      <c r="D181">
+      <c r="D181" s="4">
         <v>32.500999999999998</v>
       </c>
       <c r="E181">
         <v>32.488</v>
       </c>
-      <c r="F181">
+      <c r="F181" s="8">
         <v>32.484999999999999</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A182">
         <v>180</v>
       </c>
@@ -4034,17 +4046,17 @@
       <c r="C182">
         <v>32.414000000000001</v>
       </c>
-      <c r="D182" s="2">
+      <c r="D182" s="6">
         <v>32.527000000000001</v>
       </c>
       <c r="E182">
         <v>32.494999999999997</v>
       </c>
-      <c r="F182">
+      <c r="F182" s="8">
         <v>32.508000000000003</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A183">
         <v>181</v>
       </c>
@@ -4054,17 +4066,17 @@
       <c r="C183">
         <v>32.35</v>
       </c>
-      <c r="D183" s="2">
+      <c r="D183" s="6">
         <v>32.531999999999996</v>
       </c>
       <c r="E183">
         <v>32.499000000000002</v>
       </c>
-      <c r="F183">
+      <c r="F183" s="8">
         <v>32.46</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A184">
         <v>182</v>
       </c>
@@ -4074,17 +4086,17 @@
       <c r="C184">
         <v>32.399000000000001</v>
       </c>
-      <c r="D184">
+      <c r="D184" s="4">
         <v>32.47</v>
       </c>
       <c r="E184">
         <v>32.509</v>
       </c>
-      <c r="F184">
+      <c r="F184" s="8">
         <v>32.506</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A185">
         <v>183</v>
       </c>
@@ -4094,17 +4106,17 @@
       <c r="C185">
         <v>32.399000000000001</v>
       </c>
-      <c r="D185">
+      <c r="D185" s="4">
         <v>32.53</v>
       </c>
       <c r="E185">
         <v>32.47</v>
       </c>
-      <c r="F185" s="2">
+      <c r="F185" s="10">
         <v>32.526000000000003</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A186">
         <v>184</v>
       </c>
@@ -4114,57 +4126,57 @@
       <c r="C186">
         <v>32.378999999999998</v>
       </c>
-      <c r="D186" s="2">
+      <c r="D186" s="6">
         <v>32.552</v>
       </c>
       <c r="E186">
         <v>32.500999999999998</v>
       </c>
-      <c r="F186">
+      <c r="F186" s="8">
         <v>32.463999999999999</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A187">
         <v>185</v>
       </c>
-      <c r="B187" s="2">
+      <c r="B187" s="1">
         <v>32.639000000000003</v>
       </c>
       <c r="C187">
         <v>32.384</v>
       </c>
-      <c r="D187">
+      <c r="D187" s="4">
         <v>32.521000000000001</v>
       </c>
       <c r="E187">
         <v>32.49</v>
       </c>
-      <c r="F187">
+      <c r="F187" s="8">
         <v>32.526000000000003</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A188">
         <v>186</v>
       </c>
-      <c r="B188" s="2">
+      <c r="B188" s="1">
         <v>32.594999999999999</v>
       </c>
-      <c r="C188" s="2">
+      <c r="C188" s="1">
         <v>32.43</v>
       </c>
-      <c r="D188">
+      <c r="D188" s="4">
         <v>32.520000000000003</v>
       </c>
       <c r="E188">
         <v>32.503</v>
       </c>
-      <c r="F188" s="2">
+      <c r="F188" s="10">
         <v>32.530999999999999</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A189">
         <v>187</v>
       </c>
@@ -4174,17 +4186,17 @@
       <c r="C189">
         <v>32.417000000000002</v>
       </c>
-      <c r="D189">
+      <c r="D189" s="4">
         <v>32.533000000000001</v>
       </c>
       <c r="E189">
         <v>32.509</v>
       </c>
-      <c r="F189">
+      <c r="F189" s="8">
         <v>32.503999999999998</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A190">
         <v>188</v>
       </c>
@@ -4194,17 +4206,17 @@
       <c r="C190">
         <v>32.39</v>
       </c>
-      <c r="D190">
+      <c r="D190" s="4">
         <v>32.506999999999998</v>
       </c>
       <c r="E190">
         <v>32.497</v>
       </c>
-      <c r="F190">
+      <c r="F190" s="8">
         <v>32.523000000000003</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A191">
         <v>189</v>
       </c>
@@ -4214,17 +4226,17 @@
       <c r="C191">
         <v>32.390999999999998</v>
       </c>
-      <c r="D191">
+      <c r="D191" s="4">
         <v>32.551000000000002</v>
       </c>
       <c r="E191">
         <v>32.496000000000002</v>
       </c>
-      <c r="F191">
+      <c r="F191" s="8">
         <v>32.523000000000003</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A192">
         <v>190</v>
       </c>
@@ -4234,17 +4246,17 @@
       <c r="C192">
         <v>32.343000000000004</v>
       </c>
-      <c r="D192">
+      <c r="D192" s="4">
         <v>32.511000000000003</v>
       </c>
       <c r="E192">
         <v>32.499000000000002</v>
       </c>
-      <c r="F192">
+      <c r="F192" s="8">
         <v>32.515000000000001</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A193">
         <v>191</v>
       </c>
@@ -4254,17 +4266,17 @@
       <c r="C193">
         <v>32.42</v>
       </c>
-      <c r="D193">
+      <c r="D193" s="4">
         <v>32.508000000000003</v>
       </c>
       <c r="E193">
         <v>32.494</v>
       </c>
-      <c r="F193">
+      <c r="F193" s="8">
         <v>32.484999999999999</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A194">
         <v>192</v>
       </c>
@@ -4274,17 +4286,17 @@
       <c r="C194">
         <v>32.406999999999996</v>
       </c>
-      <c r="D194">
+      <c r="D194" s="4">
         <v>32.524000000000001</v>
       </c>
       <c r="E194">
         <v>32.494999999999997</v>
       </c>
-      <c r="F194">
+      <c r="F194" s="8">
         <v>32.506999999999998</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A195">
         <v>193</v>
       </c>
@@ -4294,17 +4306,17 @@
       <c r="C195">
         <v>32.418999999999997</v>
       </c>
-      <c r="D195" s="2">
+      <c r="D195" s="6">
         <v>32.561999999999998</v>
       </c>
-      <c r="E195" s="2">
+      <c r="E195" s="1">
         <v>32.511000000000003</v>
       </c>
-      <c r="F195">
+      <c r="F195" s="8">
         <v>32.512</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A196">
         <v>194</v>
       </c>
@@ -4314,37 +4326,37 @@
       <c r="C196">
         <v>32.408999999999999</v>
       </c>
-      <c r="D196">
+      <c r="D196" s="4">
         <v>32.523000000000003</v>
       </c>
       <c r="E196">
         <v>32.494999999999997</v>
       </c>
-      <c r="F196" s="2">
+      <c r="F196" s="10">
         <v>32.545000000000002</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A197">
         <v>195</v>
       </c>
-      <c r="B197" s="2">
+      <c r="B197" s="1">
         <v>32.598999999999997</v>
       </c>
       <c r="C197">
         <v>32.414999999999999</v>
       </c>
-      <c r="D197">
+      <c r="D197" s="4">
         <v>32.530999999999999</v>
       </c>
       <c r="E197">
         <v>32.505000000000003</v>
       </c>
-      <c r="F197">
+      <c r="F197" s="8">
         <v>32.515000000000001</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A198">
         <v>196</v>
       </c>
@@ -4354,37 +4366,37 @@
       <c r="C198">
         <v>32.415999999999997</v>
       </c>
-      <c r="D198">
+      <c r="D198" s="4">
         <v>32.545999999999999</v>
       </c>
       <c r="E198">
         <v>32.508000000000003</v>
       </c>
-      <c r="F198" s="2">
+      <c r="F198" s="10">
         <v>32.548000000000002</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A199">
         <v>197</v>
       </c>
       <c r="B199">
         <v>32.567</v>
       </c>
-      <c r="C199" s="2">
+      <c r="C199" s="1">
         <v>32.435000000000002</v>
       </c>
-      <c r="D199">
+      <c r="D199" s="4">
         <v>32.542000000000002</v>
       </c>
       <c r="E199">
         <v>32.503</v>
       </c>
-      <c r="F199">
+      <c r="F199" s="8">
         <v>32.540999999999997</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A200">
         <v>198</v>
       </c>
@@ -4394,37 +4406,37 @@
       <c r="C200">
         <v>32.417000000000002</v>
       </c>
-      <c r="D200">
+      <c r="D200" s="4">
         <v>32.529000000000003</v>
       </c>
       <c r="E200">
         <v>32.503</v>
       </c>
-      <c r="F200">
+      <c r="F200" s="8">
         <v>32.499000000000002</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A201">
         <v>199</v>
       </c>
-      <c r="B201" s="2">
+      <c r="B201" s="1">
         <v>32.652000000000001</v>
       </c>
       <c r="C201">
         <v>32.423000000000002</v>
       </c>
-      <c r="D201">
+      <c r="D201" s="4">
         <v>32.537999999999997</v>
       </c>
       <c r="E201">
         <v>32.503</v>
       </c>
-      <c r="F201">
+      <c r="F201" s="8">
         <v>32.512</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A202">
         <v>200</v>
       </c>
@@ -4434,57 +4446,57 @@
       <c r="C202">
         <v>32.418999999999997</v>
       </c>
-      <c r="D202">
+      <c r="D202" s="4">
         <v>32.524000000000001</v>
       </c>
       <c r="E202">
         <v>32.502000000000002</v>
       </c>
-      <c r="F202">
+      <c r="F202" s="8">
         <v>32.503</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A203">
         <v>201</v>
       </c>
       <c r="B203">
         <v>32.691000000000003</v>
       </c>
-      <c r="C203" s="2">
+      <c r="C203" s="1">
         <v>32.436</v>
       </c>
-      <c r="D203">
+      <c r="D203" s="4">
         <v>32.539000000000001</v>
       </c>
       <c r="E203">
         <v>32.503999999999998</v>
       </c>
-      <c r="F203">
+      <c r="F203" s="8">
         <v>32.524999999999999</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A204">
         <v>202</v>
       </c>
-      <c r="B204" s="2">
+      <c r="B204" s="1">
         <v>32.671999999999997</v>
       </c>
       <c r="C204">
         <v>32.402999999999999</v>
       </c>
-      <c r="D204">
+      <c r="D204" s="4">
         <v>32.561</v>
       </c>
       <c r="E204">
         <v>32.506999999999998</v>
       </c>
-      <c r="F204">
+      <c r="F204" s="8">
         <v>32.518000000000001</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A205">
         <v>203</v>
       </c>
@@ -4494,57 +4506,57 @@
       <c r="C205">
         <v>32.423999999999999</v>
       </c>
-      <c r="D205" s="2">
+      <c r="D205" s="6">
         <v>32.569000000000003</v>
       </c>
-      <c r="E205" s="2">
+      <c r="E205" s="1">
         <v>32.512</v>
       </c>
-      <c r="F205" s="2">
+      <c r="F205" s="10">
         <v>32.551000000000002</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A206">
         <v>204</v>
       </c>
       <c r="B206">
         <v>32.685000000000002</v>
       </c>
-      <c r="C206" s="2">
+      <c r="C206" s="1">
         <v>32.445</v>
       </c>
-      <c r="D206" s="2">
+      <c r="D206" s="6">
         <v>32.582999999999998</v>
       </c>
       <c r="E206">
         <v>32.503999999999998</v>
       </c>
-      <c r="F206">
+      <c r="F206" s="8">
         <v>32.536000000000001</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A207">
         <v>205</v>
       </c>
       <c r="B207">
         <v>32.683999999999997</v>
       </c>
-      <c r="C207" s="2">
+      <c r="C207" s="1">
         <v>32.445</v>
       </c>
-      <c r="D207">
+      <c r="D207" s="4">
         <v>32.557000000000002</v>
       </c>
       <c r="E207">
         <v>32.506</v>
       </c>
-      <c r="F207">
+      <c r="F207" s="8">
         <v>32.526000000000003</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A208">
         <v>206</v>
       </c>
@@ -4554,57 +4566,57 @@
       <c r="C208">
         <v>32.433999999999997</v>
       </c>
-      <c r="D208">
+      <c r="D208" s="4">
         <v>32.561999999999998</v>
       </c>
       <c r="E208">
         <v>32.506</v>
       </c>
-      <c r="F208">
+      <c r="F208" s="8">
         <v>32.539000000000001</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A209">
         <v>207</v>
       </c>
       <c r="B209">
         <v>32.692999999999998</v>
       </c>
-      <c r="C209" s="2">
+      <c r="C209" s="1">
         <v>32.445</v>
       </c>
-      <c r="D209">
+      <c r="D209" s="4">
         <v>32.561999999999998</v>
       </c>
       <c r="E209">
         <v>32.51</v>
       </c>
-      <c r="F209">
+      <c r="F209" s="8">
         <v>32.549999999999997</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A210">
         <v>208</v>
       </c>
-      <c r="B210" s="2">
+      <c r="B210" s="1">
         <v>32.677</v>
       </c>
-      <c r="C210" s="2">
+      <c r="C210" s="1">
         <v>32.450000000000003</v>
       </c>
-      <c r="D210">
+      <c r="D210" s="4">
         <v>32.536999999999999</v>
       </c>
       <c r="E210">
         <v>32.503999999999998</v>
       </c>
-      <c r="F210">
+      <c r="F210" s="8">
         <v>32.529000000000003</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A211">
         <v>209</v>
       </c>
@@ -4614,17 +4626,17 @@
       <c r="C211">
         <v>32.420999999999999</v>
       </c>
-      <c r="D211">
+      <c r="D211" s="4">
         <v>32.564999999999998</v>
       </c>
-      <c r="E211" s="2">
+      <c r="E211" s="1">
         <v>32.512</v>
       </c>
-      <c r="F211" s="2">
+      <c r="F211" s="10">
         <v>32.552999999999997</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A212">
         <v>210</v>
       </c>
@@ -4634,37 +4646,37 @@
       <c r="C212">
         <v>32.444000000000003</v>
       </c>
-      <c r="D212">
+      <c r="D212" s="4">
         <v>32.569000000000003</v>
       </c>
       <c r="E212">
         <v>32.51</v>
       </c>
-      <c r="F212" s="2">
+      <c r="F212" s="10">
         <v>32.570999999999998</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A213">
         <v>211</v>
       </c>
-      <c r="B213" s="2">
+      <c r="B213" s="1">
         <v>32.689</v>
       </c>
       <c r="C213">
         <v>32.444000000000003</v>
       </c>
-      <c r="D213">
+      <c r="D213" s="4">
         <v>32.567999999999998</v>
       </c>
       <c r="E213">
         <v>32.506999999999998</v>
       </c>
-      <c r="F213">
+      <c r="F213" s="8">
         <v>32.564999999999998</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A214">
         <v>212</v>
       </c>
@@ -4674,17 +4686,17 @@
       <c r="C214">
         <v>32.441000000000003</v>
       </c>
-      <c r="D214">
+      <c r="D214" s="4">
         <v>32.566000000000003</v>
       </c>
       <c r="E214">
         <v>32.505000000000003</v>
       </c>
-      <c r="F214">
+      <c r="F214" s="8">
         <v>32.561999999999998</v>
       </c>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A215">
         <v>213</v>
       </c>
@@ -4694,17 +4706,17 @@
       <c r="C215">
         <v>32.448</v>
       </c>
-      <c r="D215">
+      <c r="D215" s="4">
         <v>32.573999999999998</v>
       </c>
       <c r="E215">
         <v>32.509</v>
       </c>
-      <c r="F215" s="2">
+      <c r="F215" s="10">
         <v>32.582000000000001</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A216">
         <v>214</v>
       </c>
@@ -4714,17 +4726,17 @@
       <c r="C216">
         <v>32.43</v>
       </c>
-      <c r="D216">
+      <c r="D216" s="4">
         <v>32.567</v>
       </c>
-      <c r="E216" s="2">
+      <c r="E216" s="1">
         <v>32.512999999999998</v>
       </c>
-      <c r="F216">
+      <c r="F216" s="8">
         <v>32.543999999999997</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A217">
         <v>215</v>
       </c>
@@ -4734,17 +4746,17 @@
       <c r="C217">
         <v>32.444000000000003</v>
       </c>
-      <c r="D217">
+      <c r="D217" s="4">
         <v>32.567</v>
       </c>
       <c r="E217">
         <v>32.506999999999998</v>
       </c>
-      <c r="F217">
+      <c r="F217" s="8">
         <v>32.542000000000002</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A218">
         <v>216</v>
       </c>
@@ -4754,37 +4766,37 @@
       <c r="C218">
         <v>32.433</v>
       </c>
-      <c r="D218">
+      <c r="D218" s="4">
         <v>32.581000000000003</v>
       </c>
       <c r="E218">
         <v>32.51</v>
       </c>
-      <c r="F218">
+      <c r="F218" s="8">
         <v>32.572000000000003</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A219">
         <v>217</v>
       </c>
-      <c r="B219" s="2">
+      <c r="B219" s="1">
         <v>32.661999999999999</v>
       </c>
-      <c r="C219" s="2">
+      <c r="C219" s="1">
         <v>32.456000000000003</v>
       </c>
-      <c r="D219">
+      <c r="D219" s="4">
         <v>32.582000000000001</v>
       </c>
-      <c r="E219" s="2">
+      <c r="E219" s="1">
         <v>32.512999999999998</v>
       </c>
-      <c r="F219">
+      <c r="F219" s="8">
         <v>32.56</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A220">
         <v>218</v>
       </c>
@@ -4794,37 +4806,37 @@
       <c r="C220">
         <v>32.454999999999998</v>
       </c>
-      <c r="D220">
+      <c r="D220" s="4">
         <v>32.561</v>
       </c>
       <c r="E220">
         <v>32.506</v>
       </c>
-      <c r="F220">
+      <c r="F220" s="8">
         <v>32.579000000000001</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A221">
         <v>219</v>
       </c>
       <c r="B221">
         <v>32.694000000000003</v>
       </c>
-      <c r="C221" s="2">
+      <c r="C221" s="1">
         <v>32.462000000000003</v>
       </c>
-      <c r="D221">
+      <c r="D221" s="4">
         <v>32.57</v>
       </c>
       <c r="E221">
         <v>32.508000000000003</v>
       </c>
-      <c r="F221">
+      <c r="F221" s="8">
         <v>32.54</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A222">
         <v>220</v>
       </c>
@@ -4834,17 +4846,17 @@
       <c r="C222">
         <v>32.457999999999998</v>
       </c>
-      <c r="D222">
+      <c r="D222" s="4">
         <v>32.567</v>
       </c>
       <c r="E222">
         <v>32.406999999999996</v>
       </c>
-      <c r="F222">
+      <c r="F222" s="8">
         <v>32.545000000000002</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A223">
         <v>221</v>
       </c>
@@ -4854,77 +4866,77 @@
       <c r="C223">
         <v>32.447000000000003</v>
       </c>
-      <c r="D223" s="2">
+      <c r="D223" s="6">
         <v>32.590000000000003</v>
       </c>
       <c r="E223">
         <v>32.401000000000003</v>
       </c>
-      <c r="F223">
+      <c r="F223" s="8">
         <v>32.576000000000001</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A224">
         <v>222</v>
       </c>
       <c r="B224">
         <v>32.726999999999997</v>
       </c>
-      <c r="C224" s="2">
+      <c r="C224" s="1">
         <v>32.465000000000003</v>
       </c>
-      <c r="D224" s="2">
+      <c r="D224" s="6">
         <v>32.591999999999999</v>
       </c>
       <c r="E224">
         <v>32.463000000000001</v>
       </c>
-      <c r="F224">
+      <c r="F224" s="8">
         <v>32.563000000000002</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A225">
         <v>223</v>
       </c>
-      <c r="B225" s="2">
+      <c r="B225" s="1">
         <v>32.64</v>
       </c>
-      <c r="C225" s="2">
+      <c r="C225" s="1">
         <v>32.465000000000003</v>
       </c>
-      <c r="D225">
+      <c r="D225" s="4">
         <v>32.58</v>
       </c>
       <c r="E225">
         <v>32.393000000000001</v>
       </c>
-      <c r="F225">
+      <c r="F225" s="8">
         <v>32.563000000000002</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A226">
         <v>224</v>
       </c>
       <c r="B226">
         <v>32.704999999999998</v>
       </c>
-      <c r="C226" s="2">
+      <c r="C226" s="1">
         <v>32.472000000000001</v>
       </c>
-      <c r="D226">
+      <c r="D226" s="4">
         <v>32.576999999999998</v>
       </c>
       <c r="E226">
         <v>32.445999999999998</v>
       </c>
-      <c r="F226">
+      <c r="F226" s="8">
         <v>32.572000000000003</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A227">
         <v>225</v>
       </c>
@@ -4934,17 +4946,17 @@
       <c r="C227">
         <v>32.463000000000001</v>
       </c>
-      <c r="D227">
+      <c r="D227" s="4">
         <v>32.564</v>
       </c>
       <c r="E227">
         <v>32.451000000000001</v>
       </c>
-      <c r="F227">
+      <c r="F227" s="8">
         <v>32.543999999999997</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A228">
         <v>226</v>
       </c>
@@ -4954,17 +4966,17 @@
       <c r="C228">
         <v>32.468000000000004</v>
       </c>
-      <c r="D228">
+      <c r="D228" s="4">
         <v>32.529000000000003</v>
       </c>
       <c r="E228">
         <v>32.375999999999998</v>
       </c>
-      <c r="F228">
+      <c r="F228" s="8">
         <v>32.527000000000001</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A229">
         <v>227</v>
       </c>
@@ -4974,17 +4986,17 @@
       <c r="C229">
         <v>32.447000000000003</v>
       </c>
-      <c r="D229">
+      <c r="D229" s="4">
         <v>32.542000000000002</v>
       </c>
       <c r="E229">
         <v>32.417999999999999</v>
       </c>
-      <c r="F229">
+      <c r="F229" s="8">
         <v>32.576000000000001</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A230">
         <v>228</v>
       </c>
@@ -4994,17 +5006,17 @@
       <c r="C230">
         <v>32.450000000000003</v>
       </c>
-      <c r="D230">
+      <c r="D230" s="4">
         <v>32.57</v>
       </c>
       <c r="E230">
         <v>32.472999999999999</v>
       </c>
-      <c r="F230">
+      <c r="F230" s="8">
         <v>32.551000000000002</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A231">
         <v>229</v>
       </c>
@@ -5014,17 +5026,17 @@
       <c r="C231">
         <v>32.457999999999998</v>
       </c>
-      <c r="D231">
+      <c r="D231" s="4">
         <v>32.555999999999997</v>
       </c>
       <c r="E231">
         <v>32.459000000000003</v>
       </c>
-      <c r="F231">
+      <c r="F231" s="8">
         <v>32.558999999999997</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A232">
         <v>230</v>
       </c>
@@ -5034,17 +5046,17 @@
       <c r="C232">
         <v>32.432000000000002</v>
       </c>
-      <c r="D232">
+      <c r="D232" s="4">
         <v>32.575000000000003</v>
       </c>
       <c r="E232">
         <v>32.465000000000003</v>
       </c>
-      <c r="F232" s="2">
+      <c r="F232" s="10">
         <v>32.594999999999999</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A233">
         <v>231</v>
       </c>
@@ -5054,37 +5066,37 @@
       <c r="C233">
         <v>32.472000000000001</v>
       </c>
-      <c r="D233">
+      <c r="D233" s="4">
         <v>32.573</v>
       </c>
       <c r="E233">
         <v>32.445</v>
       </c>
-      <c r="F233">
+      <c r="F233" s="8">
         <v>32.578000000000003</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A234">
         <v>232</v>
       </c>
       <c r="B234">
         <v>32.722000000000001</v>
       </c>
-      <c r="C234" s="2">
+      <c r="C234" s="1">
         <v>32.485999999999997</v>
       </c>
-      <c r="D234">
+      <c r="D234" s="4">
         <v>32.567999999999998</v>
       </c>
       <c r="E234">
         <v>32.432000000000002</v>
       </c>
-      <c r="F234">
+      <c r="F234" s="8">
         <v>32.575000000000003</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A235">
         <v>233</v>
       </c>
@@ -5094,17 +5106,17 @@
       <c r="C235">
         <v>32.448</v>
       </c>
-      <c r="D235">
+      <c r="D235" s="4">
         <v>32.584000000000003</v>
       </c>
       <c r="E235">
         <v>32.444000000000003</v>
       </c>
-      <c r="F235">
+      <c r="F235" s="8">
         <v>32.557000000000002</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A236">
         <v>234</v>
       </c>
@@ -5114,17 +5126,17 @@
       <c r="C236">
         <v>32.439</v>
       </c>
-      <c r="D236">
+      <c r="D236" s="4">
         <v>32.567</v>
       </c>
       <c r="E236">
         <v>32.453000000000003</v>
       </c>
-      <c r="F236">
+      <c r="F236" s="8">
         <v>32.579000000000001</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A237">
         <v>235</v>
       </c>
@@ -5134,17 +5146,17 @@
       <c r="C237">
         <v>32.430999999999997</v>
       </c>
-      <c r="D237" s="2">
+      <c r="D237" s="6">
         <v>32.600999999999999</v>
       </c>
       <c r="E237">
         <v>32.448</v>
       </c>
-      <c r="F237">
+      <c r="F237" s="8">
         <v>32.585000000000001</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A238">
         <v>236</v>
       </c>
@@ -5154,17 +5166,17 @@
       <c r="C238">
         <v>32.46</v>
       </c>
-      <c r="D238">
+      <c r="D238" s="4">
         <v>32.585999999999999</v>
       </c>
       <c r="E238">
         <v>32.418999999999997</v>
       </c>
-      <c r="F238">
+      <c r="F238" s="8">
         <v>32.585000000000001</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A239">
         <v>237</v>
       </c>
@@ -5174,17 +5186,17 @@
       <c r="C239">
         <v>32.475999999999999</v>
       </c>
-      <c r="D239">
+      <c r="D239" s="4">
         <v>32.587000000000003</v>
       </c>
       <c r="E239">
         <v>32.322000000000003</v>
       </c>
-      <c r="F239">
+      <c r="F239" s="8">
         <v>32.573999999999998</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A240">
         <v>238</v>
       </c>
@@ -5194,17 +5206,17 @@
       <c r="C240">
         <v>32.482999999999997</v>
       </c>
-      <c r="D240">
+      <c r="D240" s="4">
         <v>32.570999999999998</v>
       </c>
       <c r="E240">
         <v>32.44</v>
       </c>
-      <c r="F240">
+      <c r="F240" s="8">
         <v>32.588999999999999</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A241">
         <v>239</v>
       </c>
@@ -5214,17 +5226,17 @@
       <c r="C241">
         <v>32.462000000000003</v>
       </c>
-      <c r="D241">
+      <c r="D241" s="4">
         <v>32.590000000000003</v>
       </c>
       <c r="E241">
         <v>32.475000000000001</v>
       </c>
-      <c r="F241" s="2">
+      <c r="F241" s="10">
         <v>32.597000000000001</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A242">
         <v>240</v>
       </c>
@@ -5234,17 +5246,17 @@
       <c r="C242">
         <v>32.472999999999999</v>
       </c>
-      <c r="D242">
+      <c r="D242" s="4">
         <v>32.594999999999999</v>
       </c>
       <c r="E242">
         <v>32.444000000000003</v>
       </c>
-      <c r="F242" s="2">
+      <c r="F242" s="10">
         <v>32.6</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A243">
         <v>241</v>
       </c>
@@ -5254,17 +5266,17 @@
       <c r="C243">
         <v>32.466999999999999</v>
       </c>
-      <c r="D243">
+      <c r="D243" s="4">
         <v>32.594000000000001</v>
       </c>
       <c r="E243">
         <v>32.365000000000002</v>
       </c>
-      <c r="F243">
+      <c r="F243" s="8">
         <v>32.597000000000001</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A244">
         <v>242</v>
       </c>
@@ -5274,17 +5286,17 @@
       <c r="C244">
         <v>32.462000000000003</v>
       </c>
-      <c r="D244">
+      <c r="D244" s="4">
         <v>32.564999999999998</v>
       </c>
       <c r="E244">
         <v>32.445</v>
       </c>
-      <c r="F244" s="3">
+      <c r="F244" s="10">
         <v>32.613</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A245">
         <v>243</v>
       </c>
@@ -5294,17 +5306,17 @@
       <c r="C245">
         <v>32.466999999999999</v>
       </c>
-      <c r="D245">
+      <c r="D245" s="4">
         <v>32.584000000000003</v>
       </c>
       <c r="E245">
         <v>32.438000000000002</v>
       </c>
-      <c r="F245">
+      <c r="F245" s="8">
         <v>32.597999999999999</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A246">
         <v>244</v>
       </c>
@@ -5314,17 +5326,17 @@
       <c r="C246">
         <v>32.475000000000001</v>
       </c>
-      <c r="D246">
+      <c r="D246" s="4">
         <v>32.593000000000004</v>
       </c>
       <c r="E246">
         <v>32.463999999999999</v>
       </c>
-      <c r="F246">
+      <c r="F246" s="8">
         <v>32.588000000000001</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A247">
         <v>245</v>
       </c>
@@ -5334,17 +5346,17 @@
       <c r="C247">
         <v>32.478000000000002</v>
       </c>
-      <c r="D247">
+      <c r="D247" s="4">
         <v>32.597000000000001</v>
       </c>
       <c r="E247">
         <v>32.484000000000002</v>
       </c>
-      <c r="F247">
+      <c r="F247" s="8">
         <v>32.597000000000001</v>
       </c>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A248">
         <v>246</v>
       </c>
@@ -5354,17 +5366,17 @@
       <c r="C248">
         <v>32.468000000000004</v>
       </c>
-      <c r="D248">
+      <c r="D248" s="4">
         <v>32.584000000000003</v>
       </c>
       <c r="E248">
         <v>32.466999999999999</v>
       </c>
-      <c r="F248">
+      <c r="F248" s="8">
         <v>32.585000000000001</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A249">
         <v>247</v>
       </c>
@@ -5374,17 +5386,17 @@
       <c r="C249">
         <v>32.484000000000002</v>
       </c>
-      <c r="D249">
+      <c r="D249" s="4">
         <v>32.584000000000003</v>
       </c>
       <c r="E249">
         <v>32.381999999999998</v>
       </c>
-      <c r="F249">
+      <c r="F249" s="8">
         <v>32.585000000000001</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A250">
         <v>248</v>
       </c>
@@ -5394,17 +5406,17 @@
       <c r="C250">
         <v>32.475999999999999</v>
       </c>
-      <c r="D250">
+      <c r="D250" s="4">
         <v>32.578000000000003</v>
       </c>
       <c r="E250">
         <v>32.447000000000003</v>
       </c>
-      <c r="F250">
+      <c r="F250" s="8">
         <v>32.590000000000003</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A251">
         <v>249</v>
       </c>
@@ -5414,17 +5426,17 @@
       <c r="C251">
         <v>32.472000000000001</v>
       </c>
-      <c r="D251">
+      <c r="D251" s="4">
         <v>32.585000000000001</v>
       </c>
       <c r="E251">
         <v>32.503999999999998</v>
       </c>
-      <c r="F251">
+      <c r="F251" s="8">
         <v>32.593000000000004</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A252">
         <v>250</v>
       </c>
@@ -5434,17 +5446,17 @@
       <c r="C252">
         <v>32.484000000000002</v>
       </c>
-      <c r="D252">
+      <c r="D252" s="4">
         <v>32.582999999999998</v>
       </c>
       <c r="E252">
         <v>32.506</v>
       </c>
-      <c r="F252">
+      <c r="F252" s="8">
         <v>32.600999999999999</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A253">
         <v>251</v>
       </c>
@@ -5454,17 +5466,17 @@
       <c r="C253">
         <v>32.484000000000002</v>
       </c>
-      <c r="D253">
+      <c r="D253" s="4">
         <v>32.573</v>
       </c>
       <c r="E253">
         <v>32.414999999999999</v>
       </c>
-      <c r="F253">
+      <c r="F253" s="8">
         <v>32.597000000000001</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A254">
         <v>252</v>
       </c>
@@ -5474,17 +5486,17 @@
       <c r="C254">
         <v>32.481000000000002</v>
       </c>
-      <c r="D254">
+      <c r="D254" s="4">
         <v>32.597000000000001</v>
       </c>
       <c r="E254">
         <v>32.451999999999998</v>
       </c>
-      <c r="F254">
+      <c r="F254" s="8">
         <v>32.593000000000004</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A255">
         <v>253</v>
       </c>
@@ -5494,37 +5506,37 @@
       <c r="C255">
         <v>32.475000000000001</v>
       </c>
-      <c r="D255">
+      <c r="D255" s="4">
         <v>32.595999999999997</v>
       </c>
       <c r="E255">
         <v>32.450000000000003</v>
       </c>
-      <c r="F255">
+      <c r="F255" s="8">
         <v>32.600999999999999</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A256">
         <v>254</v>
       </c>
       <c r="B256">
         <v>32.630000000000003</v>
       </c>
-      <c r="C256" s="2">
+      <c r="C256" s="1">
         <v>32.488</v>
       </c>
-      <c r="D256">
+      <c r="D256" s="4">
         <v>32.578000000000003</v>
       </c>
       <c r="E256">
         <v>32.420999999999999</v>
       </c>
-      <c r="F256">
+      <c r="F256" s="8">
         <v>32.598999999999997</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A257">
         <v>255</v>
       </c>
@@ -5534,17 +5546,17 @@
       <c r="C257">
         <v>32.478999999999999</v>
       </c>
-      <c r="D257">
+      <c r="D257" s="4">
         <v>32.588999999999999</v>
       </c>
       <c r="E257">
         <v>32.494</v>
       </c>
-      <c r="F257">
+      <c r="F257" s="8">
         <v>32.603000000000002</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A258">
         <v>256</v>
       </c>
@@ -5554,17 +5566,17 @@
       <c r="C258">
         <v>32.469000000000001</v>
       </c>
-      <c r="D258">
+      <c r="D258" s="4">
         <v>32.585000000000001</v>
       </c>
       <c r="E258">
         <v>32.485999999999997</v>
       </c>
-      <c r="F258">
+      <c r="F258" s="8">
         <v>32.598999999999997</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A259">
         <v>257</v>
       </c>
@@ -5574,17 +5586,17 @@
       <c r="C259">
         <v>32.482999999999997</v>
       </c>
-      <c r="D259">
+      <c r="D259" s="4">
         <v>32.597999999999999</v>
       </c>
       <c r="E259">
         <v>32.502000000000002</v>
       </c>
-      <c r="F259">
+      <c r="F259" s="8">
         <v>32.588000000000001</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A260">
         <v>258</v>
       </c>
@@ -5594,37 +5606,37 @@
       <c r="C260">
         <v>32.484999999999999</v>
       </c>
-      <c r="D260">
+      <c r="D260" s="4">
         <v>32.581000000000003</v>
       </c>
       <c r="E260">
         <v>32.485999999999997</v>
       </c>
-      <c r="F260">
+      <c r="F260" s="8">
         <v>32.588000000000001</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A261">
         <v>259</v>
       </c>
       <c r="B261">
         <v>32.695999999999998</v>
       </c>
-      <c r="C261" s="2">
+      <c r="C261" s="1">
         <v>32.49</v>
       </c>
-      <c r="D261">
+      <c r="D261" s="4">
         <v>32.587000000000003</v>
       </c>
       <c r="E261">
         <v>32.484000000000002</v>
       </c>
-      <c r="F261">
+      <c r="F261" s="8">
         <v>32.598999999999997</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A262">
         <v>260</v>
       </c>
@@ -5634,17 +5646,17 @@
       <c r="C262">
         <v>32.478999999999999</v>
       </c>
-      <c r="D262" s="3">
+      <c r="D262" s="6">
         <v>32.606999999999999</v>
       </c>
       <c r="E262">
         <v>32.470999999999997</v>
       </c>
-      <c r="F262">
+      <c r="F262" s="8">
         <v>32.606000000000002</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A263">
         <v>261</v>
       </c>
@@ -5654,17 +5666,17 @@
       <c r="C263">
         <v>32.482999999999997</v>
       </c>
-      <c r="D263">
+      <c r="D263" s="4">
         <v>32.600999999999999</v>
       </c>
       <c r="E263">
         <v>32.493000000000002</v>
       </c>
-      <c r="F263">
+      <c r="F263" s="8">
         <v>32.594000000000001</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A264">
         <v>262</v>
       </c>
@@ -5674,17 +5686,17 @@
       <c r="C264">
         <v>32.481000000000002</v>
       </c>
-      <c r="D264">
+      <c r="D264" s="4">
         <v>32.597000000000001</v>
       </c>
       <c r="E264">
         <v>32.460999999999999</v>
       </c>
-      <c r="F264">
+      <c r="F264" s="8">
         <v>32.606999999999999</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A265">
         <v>263</v>
       </c>
@@ -5694,17 +5706,17 @@
       <c r="C265">
         <v>32.470999999999997</v>
       </c>
-      <c r="D265">
+      <c r="D265" s="4">
         <v>32.594999999999999</v>
       </c>
       <c r="E265">
         <v>32.473999999999997</v>
       </c>
-      <c r="F265">
+      <c r="F265" s="8">
         <v>32.603999999999999</v>
       </c>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A266">
         <v>264</v>
       </c>
@@ -5714,17 +5726,17 @@
       <c r="C266">
         <v>32.470999999999997</v>
       </c>
-      <c r="D266">
+      <c r="D266" s="4">
         <v>32.597999999999999</v>
       </c>
       <c r="E266">
         <v>32.502000000000002</v>
       </c>
-      <c r="F266">
+      <c r="F266" s="8">
         <v>32.603000000000002</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A267">
         <v>265</v>
       </c>
@@ -5734,17 +5746,17 @@
       <c r="C267">
         <v>32.466000000000001</v>
       </c>
-      <c r="D267">
+      <c r="D267" s="4">
         <v>32.587000000000003</v>
       </c>
       <c r="E267">
         <v>32.502000000000002</v>
       </c>
-      <c r="F267">
+      <c r="F267" s="8">
         <v>32.604999999999997</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A268">
         <v>266</v>
       </c>
@@ -5754,37 +5766,37 @@
       <c r="C268">
         <v>32.484000000000002</v>
       </c>
-      <c r="D268">
+      <c r="D268" s="4">
         <v>32.606000000000002</v>
       </c>
       <c r="E268">
         <v>32.494</v>
       </c>
-      <c r="F268">
+      <c r="F268" s="8">
         <v>32.600999999999999</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A269">
         <v>267</v>
       </c>
       <c r="B269">
         <v>32.695999999999998</v>
       </c>
-      <c r="C269" s="2">
+      <c r="C269" s="1">
         <v>32.491999999999997</v>
       </c>
-      <c r="D269">
+      <c r="D269" s="4">
         <v>32.604999999999997</v>
       </c>
       <c r="E269">
         <v>32.5</v>
       </c>
-      <c r="F269">
+      <c r="F269" s="8">
         <v>32.601999999999997</v>
       </c>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A270">
         <v>268</v>
       </c>
@@ -5794,17 +5806,17 @@
       <c r="C270">
         <v>32.484000000000002</v>
       </c>
-      <c r="D270">
+      <c r="D270" s="4">
         <v>32.593000000000004</v>
       </c>
       <c r="E270">
         <v>32.435000000000002</v>
       </c>
-      <c r="F270">
+      <c r="F270" s="8">
         <v>32.595999999999997</v>
       </c>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A271">
         <v>269</v>
       </c>
@@ -5814,17 +5826,17 @@
       <c r="C271">
         <v>32.478000000000002</v>
       </c>
-      <c r="D271">
+      <c r="D271" s="4">
         <v>32.594000000000001</v>
       </c>
       <c r="E271">
         <v>32.506999999999998</v>
       </c>
-      <c r="F271">
+      <c r="F271" s="8">
         <v>32.606000000000002</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A272">
         <v>270</v>
       </c>
@@ -5834,17 +5846,17 @@
       <c r="C272">
         <v>32.475000000000001</v>
       </c>
-      <c r="D272">
+      <c r="D272" s="4">
         <v>32.601999999999997</v>
       </c>
       <c r="E272">
         <v>32.502000000000002</v>
       </c>
-      <c r="F272">
+      <c r="F272" s="8">
         <v>32.603999999999999</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A273">
         <v>271</v>
       </c>
@@ -5854,17 +5866,17 @@
       <c r="C273">
         <v>32.475999999999999</v>
       </c>
-      <c r="D273">
+      <c r="D273" s="4">
         <v>32.594000000000001</v>
       </c>
       <c r="E273">
         <v>32.488</v>
       </c>
-      <c r="F273">
+      <c r="F273" s="8">
         <v>32.600999999999999</v>
       </c>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A274">
         <v>272</v>
       </c>
@@ -5874,17 +5886,17 @@
       <c r="C274">
         <v>32.481000000000002</v>
       </c>
-      <c r="D274">
+      <c r="D274" s="4">
         <v>32.590000000000003</v>
       </c>
       <c r="E274">
         <v>32.505000000000003</v>
       </c>
-      <c r="F274">
+      <c r="F274" s="8">
         <v>32.604999999999997</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A275">
         <v>273</v>
       </c>
@@ -5894,17 +5906,17 @@
       <c r="C275">
         <v>32.487000000000002</v>
       </c>
-      <c r="D275">
+      <c r="D275" s="4">
         <v>32.597999999999999</v>
       </c>
       <c r="E275">
         <v>32.488</v>
       </c>
-      <c r="F275">
+      <c r="F275" s="8">
         <v>32.609000000000002</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A276">
         <v>274</v>
       </c>
@@ -5914,17 +5926,17 @@
       <c r="C276">
         <v>32.49</v>
       </c>
-      <c r="D276">
+      <c r="D276" s="4">
         <v>32.6</v>
       </c>
       <c r="E276">
         <v>32.5</v>
       </c>
-      <c r="F276">
+      <c r="F276" s="8">
         <v>32.600999999999999</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A277">
         <v>275</v>
       </c>
@@ -5934,17 +5946,17 @@
       <c r="C277">
         <v>32.485999999999997</v>
       </c>
-      <c r="D277">
+      <c r="D277" s="4">
         <v>32.6</v>
       </c>
       <c r="E277">
         <v>32.511000000000003</v>
       </c>
-      <c r="F277">
+      <c r="F277" s="8">
         <v>32.607999999999997</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A278">
         <v>276</v>
       </c>
@@ -5954,17 +5966,17 @@
       <c r="C278">
         <v>32.487000000000002</v>
       </c>
-      <c r="D278">
+      <c r="D278" s="4">
         <v>32.597999999999999</v>
       </c>
-      <c r="E278" s="2">
+      <c r="E278" s="1">
         <v>32.524999999999999</v>
       </c>
-      <c r="F278">
+      <c r="F278" s="8">
         <v>32.606999999999999</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A279">
         <v>277</v>
       </c>
@@ -5974,17 +5986,17 @@
       <c r="C279">
         <v>32.481999999999999</v>
       </c>
-      <c r="D279">
+      <c r="D279" s="4">
         <v>32.600999999999999</v>
       </c>
       <c r="E279">
         <v>32.439</v>
       </c>
-      <c r="F279">
+      <c r="F279" s="8">
         <v>32.61</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A280">
         <v>278</v>
       </c>
@@ -5994,17 +6006,17 @@
       <c r="C280">
         <v>32.484999999999999</v>
       </c>
-      <c r="D280">
+      <c r="D280" s="4">
         <v>32.601999999999997</v>
       </c>
       <c r="E280">
         <v>32.518999999999998</v>
       </c>
-      <c r="F280">
+      <c r="F280" s="8">
         <v>32.603999999999999</v>
       </c>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A281">
         <v>279</v>
       </c>
@@ -6014,17 +6026,17 @@
       <c r="C281">
         <v>32.484000000000002</v>
       </c>
-      <c r="D281">
+      <c r="D281" s="4">
         <v>32.606000000000002</v>
       </c>
       <c r="E281">
         <v>32.520000000000003</v>
       </c>
-      <c r="F281">
+      <c r="F281" s="8">
         <v>32.610999999999997</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A282">
         <v>280</v>
       </c>
@@ -6034,17 +6046,17 @@
       <c r="C282">
         <v>32.488999999999997</v>
       </c>
-      <c r="D282">
+      <c r="D282" s="4">
         <v>32.601999999999997</v>
       </c>
       <c r="E282">
         <v>32.478000000000002</v>
       </c>
-      <c r="F282">
+      <c r="F282" s="8">
         <v>32.610999999999997</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A283">
         <v>281</v>
       </c>
@@ -6054,17 +6066,17 @@
       <c r="C283">
         <v>32.488999999999997</v>
       </c>
-      <c r="D283">
+      <c r="D283" s="4">
         <v>32.598999999999997</v>
       </c>
       <c r="E283">
         <v>32.488999999999997</v>
       </c>
-      <c r="F283">
+      <c r="F283" s="8">
         <v>32.610999999999997</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A284">
         <v>282</v>
       </c>
@@ -6074,17 +6086,17 @@
       <c r="C284">
         <v>32.491</v>
       </c>
-      <c r="D284">
+      <c r="D284" s="4">
         <v>32.601999999999997</v>
       </c>
       <c r="E284">
         <v>32.518000000000001</v>
       </c>
-      <c r="F284">
+      <c r="F284" s="8">
         <v>32.613</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A285">
         <v>283</v>
       </c>
@@ -6094,17 +6106,17 @@
       <c r="C285">
         <v>32.49</v>
       </c>
-      <c r="D285">
+      <c r="D285" s="4">
         <v>32.603999999999999</v>
       </c>
       <c r="E285">
         <v>32.503999999999998</v>
       </c>
-      <c r="F285">
+      <c r="F285" s="8">
         <v>32.609000000000002</v>
       </c>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A286">
         <v>284</v>
       </c>
@@ -6114,17 +6126,17 @@
       <c r="C286">
         <v>32.488999999999997</v>
       </c>
-      <c r="D286">
+      <c r="D286" s="4">
         <v>32.594999999999999</v>
       </c>
       <c r="E286">
         <v>32.517000000000003</v>
       </c>
-      <c r="F286">
+      <c r="F286" s="8">
         <v>32.607999999999997</v>
       </c>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A287">
         <v>285</v>
       </c>
@@ -6134,17 +6146,17 @@
       <c r="C287">
         <v>32.485999999999997</v>
       </c>
-      <c r="D287">
+      <c r="D287" s="4">
         <v>32.601999999999997</v>
       </c>
       <c r="E287">
         <v>32.500999999999998</v>
       </c>
-      <c r="F287">
+      <c r="F287" s="8">
         <v>32.607999999999997</v>
       </c>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A288">
         <v>286</v>
       </c>
@@ -6154,77 +6166,77 @@
       <c r="C288">
         <v>32.488999999999997</v>
       </c>
-      <c r="D288">
+      <c r="D288" s="4">
         <v>32.601999999999997</v>
       </c>
       <c r="E288">
         <v>32.518999999999998</v>
       </c>
-      <c r="F288">
+      <c r="F288" s="8">
         <v>32.613</v>
       </c>
     </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A289">
         <v>287</v>
       </c>
-      <c r="B289" s="2">
+      <c r="B289" s="1">
         <v>32.706000000000003</v>
       </c>
       <c r="C289">
         <v>32.488</v>
       </c>
-      <c r="D289">
+      <c r="D289" s="4">
         <v>32.604999999999997</v>
       </c>
       <c r="E289">
         <v>32.506</v>
       </c>
-      <c r="F289">
+      <c r="F289" s="8">
         <v>32.612000000000002</v>
       </c>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A290">
         <v>288</v>
       </c>
       <c r="B290">
         <v>32.737000000000002</v>
       </c>
-      <c r="C290" s="2">
+      <c r="C290" s="1">
         <v>32.493000000000002</v>
       </c>
-      <c r="D290">
+      <c r="D290" s="4">
         <v>32.597000000000001</v>
       </c>
       <c r="E290">
         <v>32.475999999999999</v>
       </c>
-      <c r="F290">
+      <c r="F290" s="8">
         <v>32.609000000000002</v>
       </c>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A291">
         <v>289</v>
       </c>
-      <c r="B291" s="2">
+      <c r="B291" s="1">
         <v>32.725000000000001</v>
       </c>
       <c r="C291">
         <v>32.49</v>
       </c>
-      <c r="D291">
+      <c r="D291" s="4">
         <v>32.606999999999999</v>
       </c>
       <c r="E291">
         <v>32.51</v>
       </c>
-      <c r="F291">
+      <c r="F291" s="8">
         <v>32.61</v>
       </c>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A292">
         <v>290</v>
       </c>
@@ -6234,37 +6246,37 @@
       <c r="C292">
         <v>32.488</v>
       </c>
-      <c r="D292">
+      <c r="D292" s="4">
         <v>32.603999999999999</v>
       </c>
       <c r="E292">
         <v>32.521000000000001</v>
       </c>
-      <c r="F292">
+      <c r="F292" s="8">
         <v>32.610999999999997</v>
       </c>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A293">
         <v>291</v>
       </c>
-      <c r="B293" s="2">
+      <c r="B293" s="1">
         <v>32.71</v>
       </c>
       <c r="C293">
         <v>32.488</v>
       </c>
-      <c r="D293">
+      <c r="D293" s="4">
         <v>32.598999999999997</v>
       </c>
-      <c r="E293" s="2">
+      <c r="E293" s="1">
         <v>32.527999999999999</v>
       </c>
-      <c r="F293">
+      <c r="F293" s="8">
         <v>32.610999999999997</v>
       </c>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A294">
         <v>293</v>
       </c>
@@ -6274,17 +6286,17 @@
       <c r="C294">
         <v>32.487000000000002</v>
       </c>
-      <c r="D294">
+      <c r="D294" s="4">
         <v>32.601999999999997</v>
       </c>
       <c r="E294">
         <v>32.479999999999997</v>
       </c>
-      <c r="F294">
+      <c r="F294" s="8">
         <v>32.61</v>
       </c>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A295">
         <v>294</v>
       </c>
@@ -6294,77 +6306,77 @@
       <c r="C295">
         <v>32.49</v>
       </c>
-      <c r="D295">
+      <c r="D295" s="4">
         <v>32.6</v>
       </c>
       <c r="E295">
         <v>32.524000000000001</v>
       </c>
-      <c r="F295">
+      <c r="F295" s="8">
         <v>32.610999999999997</v>
       </c>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A296">
         <v>295</v>
       </c>
-      <c r="B296" s="2">
+      <c r="B296" s="1">
         <v>32.744999999999997</v>
       </c>
       <c r="C296">
         <v>32.487000000000002</v>
       </c>
-      <c r="D296">
+      <c r="D296" s="4">
         <v>32.6</v>
       </c>
       <c r="E296">
         <v>32.503999999999998</v>
       </c>
-      <c r="F296">
+      <c r="F296" s="8">
         <v>32.609000000000002</v>
       </c>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A297">
         <v>296</v>
       </c>
-      <c r="B297" s="2">
+      <c r="B297" s="1">
         <v>32.755000000000003</v>
       </c>
       <c r="C297">
         <v>32.49</v>
       </c>
-      <c r="D297">
+      <c r="D297" s="4">
         <v>32.6</v>
       </c>
       <c r="E297">
         <v>32.484999999999999</v>
       </c>
-      <c r="F297">
+      <c r="F297" s="8">
         <v>32.609000000000002</v>
       </c>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A298">
         <v>297</v>
       </c>
-      <c r="B298" s="2">
+      <c r="B298" s="1">
         <v>32.767000000000003</v>
       </c>
-      <c r="C298" s="3">
+      <c r="C298" s="1">
         <v>32.494999999999997</v>
       </c>
-      <c r="D298">
+      <c r="D298" s="4">
         <v>32.6</v>
       </c>
       <c r="E298">
         <v>32.514000000000003</v>
       </c>
-      <c r="F298">
+      <c r="F298" s="8">
         <v>32.606999999999999</v>
       </c>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A299">
         <v>298</v>
       </c>
@@ -6374,17 +6386,17 @@
       <c r="C299">
         <v>32.491999999999997</v>
       </c>
-      <c r="D299">
+      <c r="D299" s="4">
         <v>32.597000000000001</v>
       </c>
       <c r="E299">
         <v>32.518000000000001</v>
       </c>
-      <c r="F299">
+      <c r="F299" s="8">
         <v>32.606999999999999</v>
       </c>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A300">
         <v>299</v>
       </c>
@@ -6394,17 +6406,17 @@
       <c r="C300">
         <v>32.488</v>
       </c>
-      <c r="D300">
+      <c r="D300" s="4">
         <v>32.597000000000001</v>
       </c>
       <c r="E300">
         <v>32.469000000000001</v>
       </c>
-      <c r="F300">
+      <c r="F300" s="8">
         <v>32.606999999999999</v>
       </c>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A301">
         <v>300</v>
       </c>
@@ -6414,80 +6426,2215 @@
       <c r="C301">
         <v>32.49</v>
       </c>
-      <c r="D301">
+      <c r="D301" s="4">
         <v>32.598999999999997</v>
       </c>
       <c r="E301">
         <v>32.51</v>
       </c>
-      <c r="F301">
+      <c r="F301" s="8">
         <v>32.606000000000002</v>
       </c>
     </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="E303" s="2"/>
-    </row>
-    <row r="305" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="E305" s="2"/>
-    </row>
-    <row r="312" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B312" s="2"/>
-    </row>
-    <row r="313" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B313" s="2"/>
-      <c r="E313" s="2"/>
-    </row>
-    <row r="316" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B316" s="2"/>
-      <c r="E316" s="2"/>
-    </row>
-    <row r="318" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="E318" s="2"/>
-    </row>
-    <row r="320" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="E320" s="2"/>
-    </row>
-    <row r="321" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B321" s="2"/>
-    </row>
-    <row r="327" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B327" s="2"/>
-    </row>
-    <row r="329" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="E329" s="2"/>
-    </row>
-    <row r="343" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="E343" s="2"/>
-    </row>
-    <row r="344" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B344" s="2"/>
-    </row>
-    <row r="353" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B353" s="2"/>
-    </row>
-    <row r="365" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="E365" s="2"/>
-    </row>
-    <row r="367" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="E367" s="2"/>
-    </row>
-    <row r="377" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="E377" s="2"/>
-    </row>
-    <row r="379" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B379" s="2"/>
-    </row>
-    <row r="390" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B390" s="2"/>
-    </row>
-    <row r="392" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="E392" s="2"/>
-    </row>
-    <row r="393" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="E393" s="3"/>
-    </row>
-    <row r="407" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B407" s="3"/>
+    <row r="302" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A302">
+        <v>301</v>
+      </c>
+      <c r="B302">
+        <v>32.758000000000003</v>
+      </c>
+      <c r="C302">
+        <v>32.470999999999997</v>
+      </c>
+      <c r="D302" s="4">
+        <v>32.573999999999998</v>
+      </c>
+      <c r="E302">
+        <v>32.511000000000003</v>
+      </c>
+      <c r="F302" s="8">
+        <v>32.587000000000003</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A303">
+        <v>302</v>
+      </c>
+      <c r="B303">
+        <v>32.752000000000002</v>
+      </c>
+      <c r="C303">
+        <v>32.451999999999998</v>
+      </c>
+      <c r="D303" s="4">
+        <v>32.585000000000001</v>
+      </c>
+      <c r="E303" s="1">
+        <v>32.533000000000001</v>
+      </c>
+      <c r="F303" s="8">
+        <v>32.573999999999998</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A304">
+        <v>303</v>
+      </c>
+      <c r="B304">
+        <v>32.765000000000001</v>
+      </c>
+      <c r="C304">
+        <v>32.457000000000001</v>
+      </c>
+      <c r="D304" s="4">
+        <v>32.573999999999998</v>
+      </c>
+      <c r="E304">
+        <v>32.526000000000003</v>
+      </c>
+      <c r="F304" s="8">
+        <v>32.581000000000003</v>
+      </c>
+    </row>
+    <row r="305" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A305">
+        <v>304</v>
+      </c>
+      <c r="B305">
+        <v>32.749000000000002</v>
+      </c>
+      <c r="C305">
+        <v>32.466000000000001</v>
+      </c>
+      <c r="D305" s="4">
+        <v>32.56</v>
+      </c>
+      <c r="E305" s="1">
+        <v>32.539000000000001</v>
+      </c>
+      <c r="F305" s="8">
+        <v>32.564</v>
+      </c>
+    </row>
+    <row r="306" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A306">
+        <v>305</v>
+      </c>
+      <c r="B306">
+        <v>32.753999999999998</v>
+      </c>
+      <c r="C306">
+        <v>32.462000000000003</v>
+      </c>
+      <c r="D306" s="4">
+        <v>32.598999999999997</v>
+      </c>
+      <c r="E306">
+        <v>32.533000000000001</v>
+      </c>
+      <c r="F306" s="8">
+        <v>32.558</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A307">
+        <v>306</v>
+      </c>
+      <c r="B307">
+        <v>32.756</v>
+      </c>
+      <c r="C307">
+        <v>32.472999999999999</v>
+      </c>
+      <c r="D307" s="4">
+        <v>32.585999999999999</v>
+      </c>
+      <c r="E307">
+        <v>32.508000000000003</v>
+      </c>
+      <c r="F307" s="8">
+        <v>32.566000000000003</v>
+      </c>
+    </row>
+    <row r="308" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A308">
+        <v>307</v>
+      </c>
+      <c r="B308">
+        <v>32.756</v>
+      </c>
+      <c r="C308">
+        <v>32.476999999999997</v>
+      </c>
+      <c r="D308" s="4">
+        <v>32.578000000000003</v>
+      </c>
+      <c r="E308">
+        <v>32.536999999999999</v>
+      </c>
+      <c r="F308" s="8">
+        <v>32.604999999999997</v>
+      </c>
+    </row>
+    <row r="309" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A309">
+        <v>308</v>
+      </c>
+      <c r="B309">
+        <v>32.759</v>
+      </c>
+      <c r="C309">
+        <v>32.478000000000002</v>
+      </c>
+      <c r="D309" s="4">
+        <v>32.545000000000002</v>
+      </c>
+      <c r="E309">
+        <v>32.533999999999999</v>
+      </c>
+      <c r="F309" s="8">
+        <v>32.581000000000003</v>
+      </c>
+    </row>
+    <row r="310" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A310">
+        <v>309</v>
+      </c>
+      <c r="B310">
+        <v>32.76</v>
+      </c>
+      <c r="C310">
+        <v>32.466000000000001</v>
+      </c>
+      <c r="D310" s="4">
+        <v>32.558999999999997</v>
+      </c>
+      <c r="E310">
+        <v>32.527999999999999</v>
+      </c>
+      <c r="F310" s="8">
+        <v>32.563000000000002</v>
+      </c>
+    </row>
+    <row r="311" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A311">
+        <v>310</v>
+      </c>
+      <c r="B311">
+        <v>32.758000000000003</v>
+      </c>
+      <c r="C311">
+        <v>32.479999999999997</v>
+      </c>
+      <c r="D311" s="4">
+        <v>32.584000000000003</v>
+      </c>
+      <c r="E311">
+        <v>32.515999999999998</v>
+      </c>
+      <c r="F311" s="8">
+        <v>32.576000000000001</v>
+      </c>
+    </row>
+    <row r="312" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A312">
+        <v>311</v>
+      </c>
+      <c r="B312" s="1">
+        <v>32.771999999999998</v>
+      </c>
+      <c r="C312">
+        <v>32.448999999999998</v>
+      </c>
+      <c r="D312" s="4">
+        <v>32.578000000000003</v>
+      </c>
+      <c r="E312">
+        <v>32.536999999999999</v>
+      </c>
+      <c r="F312" s="8">
+        <v>32.6</v>
+      </c>
+    </row>
+    <row r="313" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A313">
+        <v>312</v>
+      </c>
+      <c r="B313" s="1">
+        <v>32.771999999999998</v>
+      </c>
+      <c r="C313">
+        <v>32.462000000000003</v>
+      </c>
+      <c r="D313" s="4">
+        <v>32.582999999999998</v>
+      </c>
+      <c r="E313" s="1">
+        <v>32.543999999999997</v>
+      </c>
+      <c r="F313" s="8">
+        <v>32.570999999999998</v>
+      </c>
+    </row>
+    <row r="314" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A314">
+        <v>313</v>
+      </c>
+      <c r="B314">
+        <v>32.762999999999998</v>
+      </c>
+      <c r="C314">
+        <v>32.47</v>
+      </c>
+      <c r="D314" s="4">
+        <v>32.573999999999998</v>
+      </c>
+      <c r="E314">
+        <v>32.53</v>
+      </c>
+      <c r="F314" s="8">
+        <v>32.564999999999998</v>
+      </c>
+    </row>
+    <row r="315" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A315">
+        <v>314</v>
+      </c>
+      <c r="B315">
+        <v>32.755000000000003</v>
+      </c>
+      <c r="C315">
+        <v>32.436</v>
+      </c>
+      <c r="D315" s="4">
+        <v>32.576999999999998</v>
+      </c>
+      <c r="E315">
+        <v>32.530999999999999</v>
+      </c>
+      <c r="F315" s="8">
+        <v>32.597999999999999</v>
+      </c>
+    </row>
+    <row r="316" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A316">
+        <v>315</v>
+      </c>
+      <c r="B316" s="1">
+        <v>32.777000000000001</v>
+      </c>
+      <c r="C316">
+        <v>32.484999999999999</v>
+      </c>
+      <c r="D316" s="4">
+        <v>32.578000000000003</v>
+      </c>
+      <c r="E316" s="1">
+        <v>32.543999999999997</v>
+      </c>
+      <c r="F316" s="8">
+        <v>32.573</v>
+      </c>
+    </row>
+    <row r="317" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A317">
+        <v>316</v>
+      </c>
+      <c r="B317">
+        <v>32.767000000000003</v>
+      </c>
+      <c r="C317" s="1">
+        <v>32.500999999999998</v>
+      </c>
+      <c r="D317" s="4">
+        <v>32.561</v>
+      </c>
+      <c r="E317">
+        <v>32.526000000000003</v>
+      </c>
+      <c r="F317" s="8">
+        <v>32.594000000000001</v>
+      </c>
+    </row>
+    <row r="318" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A318">
+        <v>317</v>
+      </c>
+      <c r="B318">
+        <v>32.761000000000003</v>
+      </c>
+      <c r="C318">
+        <v>32.451999999999998</v>
+      </c>
+      <c r="D318" s="4">
+        <v>32.578000000000003</v>
+      </c>
+      <c r="E318" s="1">
+        <v>32.549999999999997</v>
+      </c>
+      <c r="F318" s="8">
+        <v>32.58</v>
+      </c>
+    </row>
+    <row r="319" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A319">
+        <v>318</v>
+      </c>
+      <c r="B319">
+        <v>32.753</v>
+      </c>
+      <c r="C319">
+        <v>32.441000000000003</v>
+      </c>
+      <c r="D319" s="4">
+        <v>32.573</v>
+      </c>
+      <c r="E319">
+        <v>32.530999999999999</v>
+      </c>
+      <c r="F319" s="8">
+        <v>32.576000000000001</v>
+      </c>
+    </row>
+    <row r="320" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A320">
+        <v>319</v>
+      </c>
+      <c r="B320">
+        <v>32.771999999999998</v>
+      </c>
+      <c r="C320">
+        <v>32.448</v>
+      </c>
+      <c r="D320" s="4">
+        <v>32.564999999999998</v>
+      </c>
+      <c r="E320" s="1">
+        <v>32.554000000000002</v>
+      </c>
+      <c r="F320" s="8">
+        <v>32.591999999999999</v>
+      </c>
+    </row>
+    <row r="321" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A321">
+        <v>320</v>
+      </c>
+      <c r="B321" s="1">
+        <v>32.777999999999999</v>
+      </c>
+      <c r="C321">
+        <v>32.468000000000004</v>
+      </c>
+      <c r="D321" s="4">
+        <v>32.594999999999999</v>
+      </c>
+      <c r="E321">
+        <v>32.524000000000001</v>
+      </c>
+      <c r="F321" s="8">
+        <v>32.585000000000001</v>
+      </c>
+    </row>
+    <row r="322" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A322">
+        <v>321</v>
+      </c>
+      <c r="B322">
+        <v>32.771000000000001</v>
+      </c>
+      <c r="C322">
+        <v>32.479999999999997</v>
+      </c>
+      <c r="D322" s="4">
+        <v>32.597000000000001</v>
+      </c>
+      <c r="E322">
+        <v>32.530999999999999</v>
+      </c>
+      <c r="F322" s="8">
+        <v>32.584000000000003</v>
+      </c>
+    </row>
+    <row r="323" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A323">
+        <v>322</v>
+      </c>
+      <c r="B323">
+        <v>32.771000000000001</v>
+      </c>
+      <c r="C323">
+        <v>32.49</v>
+      </c>
+      <c r="D323" s="4">
+        <v>32.595999999999997</v>
+      </c>
+      <c r="E323">
+        <v>32.536999999999999</v>
+      </c>
+      <c r="F323" s="8">
+        <v>32.588999999999999</v>
+      </c>
+    </row>
+    <row r="324" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A324">
+        <v>323</v>
+      </c>
+      <c r="B324">
+        <v>32.768999999999998</v>
+      </c>
+      <c r="C324">
+        <v>32.470999999999997</v>
+      </c>
+      <c r="D324" s="4">
+        <v>32.548999999999999</v>
+      </c>
+      <c r="E324">
+        <v>32.533999999999999</v>
+      </c>
+      <c r="F324" s="8">
+        <v>32.594999999999999</v>
+      </c>
+    </row>
+    <row r="325" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A325">
+        <v>324</v>
+      </c>
+      <c r="B325">
+        <v>32.750999999999998</v>
+      </c>
+      <c r="C325">
+        <v>32.478999999999999</v>
+      </c>
+      <c r="D325" s="4">
+        <v>32.588999999999999</v>
+      </c>
+      <c r="E325">
+        <v>32.524999999999999</v>
+      </c>
+      <c r="F325" s="8">
+        <v>32.573999999999998</v>
+      </c>
+    </row>
+    <row r="326" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A326">
+        <v>325</v>
+      </c>
+      <c r="B326">
+        <v>32.72</v>
+      </c>
+      <c r="C326">
+        <v>32.475000000000001</v>
+      </c>
+      <c r="D326" s="4">
+        <v>32.595999999999997</v>
+      </c>
+      <c r="E326">
+        <v>32.537999999999997</v>
+      </c>
+      <c r="F326" s="8">
+        <v>32.601999999999997</v>
+      </c>
+    </row>
+    <row r="327" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A327">
+        <v>326</v>
+      </c>
+      <c r="B327" s="1">
+        <v>32.783000000000001</v>
+      </c>
+      <c r="C327">
+        <v>32.468000000000004</v>
+      </c>
+      <c r="D327" s="4">
+        <v>32.590000000000003</v>
+      </c>
+      <c r="E327">
+        <v>32.509</v>
+      </c>
+      <c r="F327" s="8">
+        <v>32.585000000000001</v>
+      </c>
+    </row>
+    <row r="328" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A328">
+        <v>327</v>
+      </c>
+      <c r="B328">
+        <v>32.780999999999999</v>
+      </c>
+      <c r="C328">
+        <v>32.476999999999997</v>
+      </c>
+      <c r="D328" s="4">
+        <v>32.584000000000003</v>
+      </c>
+      <c r="E328">
+        <v>32.537999999999997</v>
+      </c>
+      <c r="F328" s="8">
+        <v>32.588999999999999</v>
+      </c>
+    </row>
+    <row r="329" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A329">
+        <v>328</v>
+      </c>
+      <c r="B329">
+        <v>32.76</v>
+      </c>
+      <c r="C329">
+        <v>32.481999999999999</v>
+      </c>
+      <c r="D329" s="4">
+        <v>32.590000000000003</v>
+      </c>
+      <c r="E329" s="1">
+        <v>32.558</v>
+      </c>
+      <c r="F329" s="8">
+        <v>32.594000000000001</v>
+      </c>
+    </row>
+    <row r="330" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A330">
+        <v>329</v>
+      </c>
+      <c r="B330">
+        <v>32.774000000000001</v>
+      </c>
+      <c r="C330">
+        <v>32.468000000000004</v>
+      </c>
+      <c r="D330" s="4">
+        <v>32.590000000000003</v>
+      </c>
+      <c r="E330">
+        <v>32.530999999999999</v>
+      </c>
+      <c r="F330" s="8">
+        <v>32.585999999999999</v>
+      </c>
+    </row>
+    <row r="331" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A331">
+        <v>330</v>
+      </c>
+      <c r="B331">
+        <v>32.767000000000003</v>
+      </c>
+      <c r="C331">
+        <v>32.484000000000002</v>
+      </c>
+      <c r="D331" s="4">
+        <v>32.587000000000003</v>
+      </c>
+      <c r="E331">
+        <v>32.527000000000001</v>
+      </c>
+      <c r="F331" s="8">
+        <v>32.585000000000001</v>
+      </c>
+    </row>
+    <row r="332" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A332">
+        <v>331</v>
+      </c>
+      <c r="B332">
+        <v>32.755000000000003</v>
+      </c>
+      <c r="C332">
+        <v>32.493000000000002</v>
+      </c>
+      <c r="D332" s="4">
+        <v>32.588000000000001</v>
+      </c>
+      <c r="E332">
+        <v>32.521000000000001</v>
+      </c>
+      <c r="F332" s="8">
+        <v>32.595999999999997</v>
+      </c>
+    </row>
+    <row r="333" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A333">
+        <v>332</v>
+      </c>
+      <c r="B333">
+        <v>32.768000000000001</v>
+      </c>
+      <c r="C333">
+        <v>32.482999999999997</v>
+      </c>
+      <c r="D333" s="4">
+        <v>32.600999999999999</v>
+      </c>
+      <c r="E333">
+        <v>32.543999999999997</v>
+      </c>
+      <c r="F333" s="8">
+        <v>32.598999999999997</v>
+      </c>
+    </row>
+    <row r="334" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A334">
+        <v>333</v>
+      </c>
+      <c r="B334">
+        <v>32.765999999999998</v>
+      </c>
+      <c r="C334">
+        <v>32.476999999999997</v>
+      </c>
+      <c r="D334" s="4">
+        <v>32.597999999999999</v>
+      </c>
+      <c r="E334">
+        <v>32.552999999999997</v>
+      </c>
+      <c r="F334" s="8">
+        <v>32.594000000000001</v>
+      </c>
+    </row>
+    <row r="335" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A335">
+        <v>334</v>
+      </c>
+      <c r="B335">
+        <v>32.76</v>
+      </c>
+      <c r="C335">
+        <v>32.482999999999997</v>
+      </c>
+      <c r="D335" s="4">
+        <v>32.591000000000001</v>
+      </c>
+      <c r="E335">
+        <v>32.542999999999999</v>
+      </c>
+      <c r="F335" s="8">
+        <v>32.588999999999999</v>
+      </c>
+    </row>
+    <row r="336" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A336">
+        <v>335</v>
+      </c>
+      <c r="B336">
+        <v>32.762999999999998</v>
+      </c>
+      <c r="C336">
+        <v>32.481000000000002</v>
+      </c>
+      <c r="D336" s="4">
+        <v>32.594000000000001</v>
+      </c>
+      <c r="E336">
+        <v>32.530999999999999</v>
+      </c>
+      <c r="F336" s="8">
+        <v>32.593000000000004</v>
+      </c>
+    </row>
+    <row r="337" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A337">
+        <v>336</v>
+      </c>
+      <c r="B337">
+        <v>32.768000000000001</v>
+      </c>
+      <c r="C337">
+        <v>32.472999999999999</v>
+      </c>
+      <c r="D337" s="4">
+        <v>32.598999999999997</v>
+      </c>
+      <c r="E337">
+        <v>32.548000000000002</v>
+      </c>
+      <c r="F337" s="8">
+        <v>32.597000000000001</v>
+      </c>
+    </row>
+    <row r="338" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A338">
+        <v>337</v>
+      </c>
+      <c r="B338">
+        <v>32.767000000000003</v>
+      </c>
+      <c r="C338" s="1">
+        <v>32.503</v>
+      </c>
+      <c r="D338" s="4">
+        <v>32.6</v>
+      </c>
+      <c r="E338">
+        <v>32.539000000000001</v>
+      </c>
+      <c r="F338" s="8">
+        <v>32.585999999999999</v>
+      </c>
+    </row>
+    <row r="339" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A339">
+        <v>338</v>
+      </c>
+      <c r="B339">
+        <v>32.765000000000001</v>
+      </c>
+      <c r="C339">
+        <v>32.466000000000001</v>
+      </c>
+      <c r="D339" s="4">
+        <v>32.603000000000002</v>
+      </c>
+      <c r="E339">
+        <v>32.521999999999998</v>
+      </c>
+      <c r="F339" s="8">
+        <v>32.585000000000001</v>
+      </c>
+    </row>
+    <row r="340" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A340">
+        <v>339</v>
+      </c>
+      <c r="B340">
+        <v>32.738999999999997</v>
+      </c>
+      <c r="C340">
+        <v>32.472000000000001</v>
+      </c>
+      <c r="D340" s="4">
+        <v>32.601999999999997</v>
+      </c>
+      <c r="E340">
+        <v>32.524999999999999</v>
+      </c>
+      <c r="F340" s="8">
+        <v>32.609000000000002</v>
+      </c>
+    </row>
+    <row r="341" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A341">
+        <v>340</v>
+      </c>
+      <c r="B341">
+        <v>32.773000000000003</v>
+      </c>
+      <c r="C341" s="1">
+        <v>32.503</v>
+      </c>
+      <c r="D341" s="4">
+        <v>32.597999999999999</v>
+      </c>
+      <c r="E341">
+        <v>32.545000000000002</v>
+      </c>
+      <c r="F341" s="8">
+        <v>32.606000000000002</v>
+      </c>
+    </row>
+    <row r="342" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A342">
+        <v>341</v>
+      </c>
+      <c r="B342">
+        <v>32.731999999999999</v>
+      </c>
+      <c r="C342">
+        <v>32.499000000000002</v>
+      </c>
+      <c r="D342" s="4">
+        <v>32.601999999999997</v>
+      </c>
+      <c r="E342">
+        <v>32.524999999999999</v>
+      </c>
+      <c r="F342" s="8">
+        <v>32.590000000000003</v>
+      </c>
+    </row>
+    <row r="343" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A343">
+        <v>342</v>
+      </c>
+      <c r="B343">
+        <v>32.752000000000002</v>
+      </c>
+      <c r="C343">
+        <v>32.475999999999999</v>
+      </c>
+      <c r="D343" s="6">
+        <v>32.613</v>
+      </c>
+      <c r="E343" s="1">
+        <v>32.561999999999998</v>
+      </c>
+      <c r="F343" s="8">
+        <v>32.595999999999997</v>
+      </c>
+    </row>
+    <row r="344" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A344">
+        <v>343</v>
+      </c>
+      <c r="B344" s="1">
+        <v>32.786999999999999</v>
+      </c>
+      <c r="C344">
+        <v>32.468000000000004</v>
+      </c>
+      <c r="D344" s="4">
+        <v>32.585999999999999</v>
+      </c>
+      <c r="E344">
+        <v>32.537999999999997</v>
+      </c>
+      <c r="F344" s="8">
+        <v>32.598999999999997</v>
+      </c>
+    </row>
+    <row r="345" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A345">
+        <v>344</v>
+      </c>
+      <c r="B345">
+        <v>32.758000000000003</v>
+      </c>
+      <c r="C345">
+        <v>32.500999999999998</v>
+      </c>
+      <c r="D345" s="4">
+        <v>32.594000000000001</v>
+      </c>
+      <c r="E345">
+        <v>32.561</v>
+      </c>
+      <c r="F345" s="8">
+        <v>32.610999999999997</v>
+      </c>
+    </row>
+    <row r="346" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A346">
+        <v>345</v>
+      </c>
+      <c r="B346">
+        <v>32.777999999999999</v>
+      </c>
+      <c r="C346" s="2">
+        <v>32.511000000000003</v>
+      </c>
+      <c r="D346" s="4">
+        <v>32.594000000000001</v>
+      </c>
+      <c r="E346">
+        <v>32.56</v>
+      </c>
+      <c r="F346" s="8">
+        <v>32.601999999999997</v>
+      </c>
+    </row>
+    <row r="347" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A347">
+        <v>346</v>
+      </c>
+      <c r="B347">
+        <v>32.768000000000001</v>
+      </c>
+      <c r="C347">
+        <v>32.503999999999998</v>
+      </c>
+      <c r="D347" s="4">
+        <v>32.6</v>
+      </c>
+      <c r="E347">
+        <v>32.557000000000002</v>
+      </c>
+      <c r="F347" s="8">
+        <v>32.594000000000001</v>
+      </c>
+    </row>
+    <row r="348" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A348">
+        <v>347</v>
+      </c>
+      <c r="B348">
+        <v>32.764000000000003</v>
+      </c>
+      <c r="C348">
+        <v>32.468000000000004</v>
+      </c>
+      <c r="D348" s="4">
+        <v>32.601999999999997</v>
+      </c>
+      <c r="E348">
+        <v>32.536999999999999</v>
+      </c>
+      <c r="F348" s="8">
+        <v>32.6</v>
+      </c>
+    </row>
+    <row r="349" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A349">
+        <v>348</v>
+      </c>
+      <c r="B349">
+        <v>32.756999999999998</v>
+      </c>
+      <c r="C349">
+        <v>32.49</v>
+      </c>
+      <c r="D349" s="4">
+        <v>32.594000000000001</v>
+      </c>
+      <c r="E349">
+        <v>32.549999999999997</v>
+      </c>
+      <c r="F349" s="8">
+        <v>32.593000000000004</v>
+      </c>
+    </row>
+    <row r="350" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A350">
+        <v>349</v>
+      </c>
+      <c r="B350">
+        <v>32.762</v>
+      </c>
+      <c r="C350">
+        <v>32.482999999999997</v>
+      </c>
+      <c r="D350" s="4">
+        <v>32.590000000000003</v>
+      </c>
+      <c r="E350">
+        <v>32.551000000000002</v>
+      </c>
+      <c r="F350" s="8">
+        <v>32.606999999999999</v>
+      </c>
+    </row>
+    <row r="351" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A351">
+        <v>350</v>
+      </c>
+      <c r="B351">
+        <v>32.781999999999996</v>
+      </c>
+      <c r="C351">
+        <v>32.496000000000002</v>
+      </c>
+      <c r="D351" s="4">
+        <v>32.6</v>
+      </c>
+      <c r="E351">
+        <v>32.554000000000002</v>
+      </c>
+      <c r="F351" s="8">
+        <v>32.590000000000003</v>
+      </c>
+    </row>
+    <row r="352" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A352">
+        <v>351</v>
+      </c>
+      <c r="B352">
+        <v>32.78</v>
+      </c>
+      <c r="C352">
+        <v>32.497</v>
+      </c>
+      <c r="D352" s="4">
+        <v>32.610999999999997</v>
+      </c>
+      <c r="E352">
+        <v>32.548999999999999</v>
+      </c>
+      <c r="F352" s="8">
+        <v>32.6</v>
+      </c>
+    </row>
+    <row r="353" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A353">
+        <v>352</v>
+      </c>
+      <c r="B353" s="1">
+        <v>32.792999999999999</v>
+      </c>
+      <c r="C353">
+        <v>32.478999999999999</v>
+      </c>
+      <c r="D353" s="4">
+        <v>32.603000000000002</v>
+      </c>
+      <c r="E353">
+        <v>32.539000000000001</v>
+      </c>
+      <c r="F353" s="8">
+        <v>32.609000000000002</v>
+      </c>
+    </row>
+    <row r="354" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A354">
+        <v>353</v>
+      </c>
+      <c r="B354">
+        <v>32.784999999999997</v>
+      </c>
+      <c r="C354">
+        <v>32.472999999999999</v>
+      </c>
+      <c r="D354" s="4">
+        <v>32.606999999999999</v>
+      </c>
+      <c r="E354">
+        <v>32.545000000000002</v>
+      </c>
+      <c r="F354" s="8">
+        <v>32.594000000000001</v>
+      </c>
+    </row>
+    <row r="355" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A355">
+        <v>354</v>
+      </c>
+      <c r="B355">
+        <v>32.768999999999998</v>
+      </c>
+      <c r="C355">
+        <v>32.493000000000002</v>
+      </c>
+      <c r="D355" s="4">
+        <v>32.601999999999997</v>
+      </c>
+      <c r="E355">
+        <v>32.552999999999997</v>
+      </c>
+      <c r="F355" s="11">
+        <v>32.622999999999998</v>
+      </c>
+    </row>
+    <row r="356" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A356">
+        <v>355</v>
+      </c>
+      <c r="B356">
+        <v>32.774000000000001</v>
+      </c>
+      <c r="C356">
+        <v>32.491999999999997</v>
+      </c>
+      <c r="D356" s="6">
+        <v>32.615000000000002</v>
+      </c>
+      <c r="E356">
+        <v>32.548999999999999</v>
+      </c>
+      <c r="F356" s="8">
+        <v>32.6</v>
+      </c>
+    </row>
+    <row r="357" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A357">
+        <v>356</v>
+      </c>
+      <c r="B357">
+        <v>32.771999999999998</v>
+      </c>
+      <c r="C357">
+        <v>32.494999999999997</v>
+      </c>
+      <c r="D357" s="6">
+        <v>32.616999999999997</v>
+      </c>
+      <c r="E357">
+        <v>32.555</v>
+      </c>
+      <c r="F357" s="8">
+        <v>32.61</v>
+      </c>
+    </row>
+    <row r="358" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A358">
+        <v>357</v>
+      </c>
+      <c r="B358">
+        <v>32.776000000000003</v>
+      </c>
+      <c r="C358">
+        <v>32.488</v>
+      </c>
+      <c r="D358" s="4">
+        <v>32.606999999999999</v>
+      </c>
+      <c r="E358">
+        <v>32.557000000000002</v>
+      </c>
+      <c r="F358" s="8">
+        <v>32.607999999999997</v>
+      </c>
+    </row>
+    <row r="359" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A359">
+        <v>358</v>
+      </c>
+      <c r="B359">
+        <v>32.768999999999998</v>
+      </c>
+      <c r="C359">
+        <v>32.499000000000002</v>
+      </c>
+      <c r="D359" s="4">
+        <v>32.597999999999999</v>
+      </c>
+      <c r="E359">
+        <v>32.551000000000002</v>
+      </c>
+      <c r="F359" s="8">
+        <v>32.61</v>
+      </c>
+    </row>
+    <row r="360" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A360">
+        <v>359</v>
+      </c>
+      <c r="B360">
+        <v>32.786999999999999</v>
+      </c>
+      <c r="C360">
+        <v>32.497</v>
+      </c>
+      <c r="D360" s="4">
+        <v>32.600999999999999</v>
+      </c>
+      <c r="E360">
+        <v>32.557000000000002</v>
+      </c>
+      <c r="F360" s="8">
+        <v>32.616</v>
+      </c>
+    </row>
+    <row r="361" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A361">
+        <v>360</v>
+      </c>
+      <c r="B361">
+        <v>32.79</v>
+      </c>
+      <c r="C361">
+        <v>32.479999999999997</v>
+      </c>
+      <c r="D361" s="4">
+        <v>32.597999999999999</v>
+      </c>
+      <c r="E361">
+        <v>32.549999999999997</v>
+      </c>
+      <c r="F361" s="8">
+        <v>32.621000000000002</v>
+      </c>
+    </row>
+    <row r="362" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A362">
+        <v>361</v>
+      </c>
+      <c r="B362">
+        <v>32.765999999999998</v>
+      </c>
+      <c r="C362">
+        <v>32.494</v>
+      </c>
+      <c r="D362" s="4">
+        <v>32.591999999999999</v>
+      </c>
+      <c r="E362">
+        <v>32.552999999999997</v>
+      </c>
+      <c r="F362" s="8">
+        <v>32.616</v>
+      </c>
+    </row>
+    <row r="363" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A363">
+        <v>362</v>
+      </c>
+      <c r="B363">
+        <v>32.777999999999999</v>
+      </c>
+      <c r="C363">
+        <v>32.5</v>
+      </c>
+      <c r="D363" s="4">
+        <v>32.606999999999999</v>
+      </c>
+      <c r="E363">
+        <v>32.552</v>
+      </c>
+      <c r="F363" s="8">
+        <v>32.607999999999997</v>
+      </c>
+    </row>
+    <row r="364" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A364">
+        <v>363</v>
+      </c>
+      <c r="B364">
+        <v>32.783000000000001</v>
+      </c>
+      <c r="C364">
+        <v>32.488999999999997</v>
+      </c>
+      <c r="D364" s="4">
+        <v>32.601999999999997</v>
+      </c>
+      <c r="E364">
+        <v>32.558</v>
+      </c>
+      <c r="F364" s="8">
+        <v>32.606999999999999</v>
+      </c>
+    </row>
+    <row r="365" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A365">
+        <v>364</v>
+      </c>
+      <c r="B365">
+        <v>32.789000000000001</v>
+      </c>
+      <c r="C365">
+        <v>32.493000000000002</v>
+      </c>
+      <c r="D365" s="4">
+        <v>32.604999999999997</v>
+      </c>
+      <c r="E365" s="1">
+        <v>32.563000000000002</v>
+      </c>
+      <c r="F365" s="8">
+        <v>32.606999999999999</v>
+      </c>
+    </row>
+    <row r="366" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A366">
+        <v>365</v>
+      </c>
+      <c r="B366">
+        <v>32.777000000000001</v>
+      </c>
+      <c r="C366">
+        <v>32.487000000000002</v>
+      </c>
+      <c r="D366" s="4">
+        <v>32.595999999999997</v>
+      </c>
+      <c r="E366">
+        <v>32.549999999999997</v>
+      </c>
+      <c r="F366" s="8">
+        <v>32.612000000000002</v>
+      </c>
+    </row>
+    <row r="367" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A367">
+        <v>366</v>
+      </c>
+      <c r="B367">
+        <v>32.784999999999997</v>
+      </c>
+      <c r="C367">
+        <v>32.491999999999997</v>
+      </c>
+      <c r="D367" s="4">
+        <v>32.604999999999997</v>
+      </c>
+      <c r="E367" s="1">
+        <v>32.567</v>
+      </c>
+      <c r="F367" s="8">
+        <v>32.606000000000002</v>
+      </c>
+    </row>
+    <row r="368" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A368">
+        <v>367</v>
+      </c>
+      <c r="B368">
+        <v>32.774999999999999</v>
+      </c>
+      <c r="C368">
+        <v>32.494</v>
+      </c>
+      <c r="D368" s="4">
+        <v>32.597999999999999</v>
+      </c>
+      <c r="E368">
+        <v>32.555</v>
+      </c>
+      <c r="F368" s="8">
+        <v>32.604999999999997</v>
+      </c>
+    </row>
+    <row r="369" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A369">
+        <v>368</v>
+      </c>
+      <c r="B369">
+        <v>32.781999999999996</v>
+      </c>
+      <c r="C369">
+        <v>32.496000000000002</v>
+      </c>
+      <c r="D369" s="4">
+        <v>32.616</v>
+      </c>
+      <c r="E369">
+        <v>32.545000000000002</v>
+      </c>
+      <c r="F369" s="8">
+        <v>32.61</v>
+      </c>
+    </row>
+    <row r="370" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A370">
+        <v>369</v>
+      </c>
+      <c r="B370">
+        <v>32.784999999999997</v>
+      </c>
+      <c r="C370">
+        <v>32.499000000000002</v>
+      </c>
+      <c r="D370" s="6">
+        <v>32.619</v>
+      </c>
+      <c r="E370">
+        <v>32.552999999999997</v>
+      </c>
+      <c r="F370" s="8">
+        <v>32.615000000000002</v>
+      </c>
+    </row>
+    <row r="371" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A371">
+        <v>370</v>
+      </c>
+      <c r="B371">
+        <v>32.789000000000001</v>
+      </c>
+      <c r="C371">
+        <v>32.49</v>
+      </c>
+      <c r="D371" s="4">
+        <v>32.609000000000002</v>
+      </c>
+      <c r="E371">
+        <v>32.548999999999999</v>
+      </c>
+      <c r="F371" s="8">
+        <v>32.606000000000002</v>
+      </c>
+    </row>
+    <row r="372" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A372">
+        <v>371</v>
+      </c>
+      <c r="B372">
+        <v>32.78</v>
+      </c>
+      <c r="C372">
+        <v>32.484000000000002</v>
+      </c>
+      <c r="D372" s="4">
+        <v>32.606999999999999</v>
+      </c>
+      <c r="E372">
+        <v>32.552999999999997</v>
+      </c>
+      <c r="F372" s="8">
+        <v>32.610999999999997</v>
+      </c>
+    </row>
+    <row r="373" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A373">
+        <v>372</v>
+      </c>
+      <c r="B373">
+        <v>32.784999999999997</v>
+      </c>
+      <c r="C373">
+        <v>32.488999999999997</v>
+      </c>
+      <c r="D373" s="7">
+        <v>32.621000000000002</v>
+      </c>
+      <c r="E373">
+        <v>32.564</v>
+      </c>
+      <c r="F373" s="8">
+        <v>32.600999999999999</v>
+      </c>
+    </row>
+    <row r="374" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A374">
+        <v>373</v>
+      </c>
+      <c r="B374">
+        <v>32.786000000000001</v>
+      </c>
+      <c r="C374">
+        <v>32.494</v>
+      </c>
+      <c r="D374" s="4">
+        <v>32.600999999999999</v>
+      </c>
+      <c r="E374">
+        <v>32.566000000000003</v>
+      </c>
+      <c r="F374" s="8">
+        <v>32.613</v>
+      </c>
+    </row>
+    <row r="375" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A375">
+        <v>374</v>
+      </c>
+      <c r="B375">
+        <v>32.792000000000002</v>
+      </c>
+      <c r="C375">
+        <v>32.494</v>
+      </c>
+      <c r="D375" s="4">
+        <v>32.607999999999997</v>
+      </c>
+      <c r="E375">
+        <v>32.561</v>
+      </c>
+      <c r="F375" s="8">
+        <v>32.604999999999997</v>
+      </c>
+    </row>
+    <row r="376" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A376">
+        <v>375</v>
+      </c>
+      <c r="B376">
+        <v>32.789000000000001</v>
+      </c>
+      <c r="C376">
+        <v>32.497999999999998</v>
+      </c>
+      <c r="D376" s="4">
+        <v>32.609000000000002</v>
+      </c>
+      <c r="E376">
+        <v>32.561</v>
+      </c>
+      <c r="F376" s="8">
+        <v>32.615000000000002</v>
+      </c>
+    </row>
+    <row r="377" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A377">
+        <v>376</v>
+      </c>
+      <c r="B377">
+        <v>32.779000000000003</v>
+      </c>
+      <c r="C377">
+        <v>32.505000000000003</v>
+      </c>
+      <c r="D377" s="4">
+        <v>32.61</v>
+      </c>
+      <c r="E377" s="1">
+        <v>32.570999999999998</v>
+      </c>
+      <c r="F377" s="8">
+        <v>32.606000000000002</v>
+      </c>
+    </row>
+    <row r="378" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A378">
+        <v>377</v>
+      </c>
+      <c r="B378">
+        <v>32.78</v>
+      </c>
+      <c r="C378">
+        <v>32.497</v>
+      </c>
+      <c r="D378" s="4">
+        <v>32.61</v>
+      </c>
+      <c r="E378">
+        <v>32.569000000000003</v>
+      </c>
+      <c r="F378" s="8">
+        <v>32.616999999999997</v>
+      </c>
+    </row>
+    <row r="379" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A379">
+        <v>378</v>
+      </c>
+      <c r="B379" s="1">
+        <v>32.793999999999997</v>
+      </c>
+      <c r="C379">
+        <v>32.493000000000002</v>
+      </c>
+      <c r="D379" s="4">
+        <v>32.61</v>
+      </c>
+      <c r="E379">
+        <v>32.564</v>
+      </c>
+      <c r="F379" s="8">
+        <v>32.610999999999997</v>
+      </c>
+    </row>
+    <row r="380" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A380">
+        <v>379</v>
+      </c>
+      <c r="B380">
+        <v>32.789000000000001</v>
+      </c>
+      <c r="C380">
+        <v>32.497</v>
+      </c>
+      <c r="D380" s="4">
+        <v>32.603000000000002</v>
+      </c>
+      <c r="E380">
+        <v>32.561</v>
+      </c>
+      <c r="F380" s="8">
+        <v>32.612000000000002</v>
+      </c>
+    </row>
+    <row r="381" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A381">
+        <v>380</v>
+      </c>
+      <c r="B381">
+        <v>32.780999999999999</v>
+      </c>
+      <c r="C381">
+        <v>32.497</v>
+      </c>
+      <c r="D381" s="4">
+        <v>32.6</v>
+      </c>
+      <c r="E381">
+        <v>32.566000000000003</v>
+      </c>
+      <c r="F381" s="8">
+        <v>32.619999999999997</v>
+      </c>
+    </row>
+    <row r="382" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A382">
+        <v>381</v>
+      </c>
+      <c r="B382">
+        <v>32.777000000000001</v>
+      </c>
+      <c r="C382">
+        <v>32.499000000000002</v>
+      </c>
+      <c r="D382" s="4">
+        <v>32.601999999999997</v>
+      </c>
+      <c r="E382">
+        <v>32.552999999999997</v>
+      </c>
+      <c r="F382" s="8">
+        <v>32.613999999999997</v>
+      </c>
+    </row>
+    <row r="383" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A383">
+        <v>382</v>
+      </c>
+      <c r="B383">
+        <v>32.793999999999997</v>
+      </c>
+      <c r="C383">
+        <v>32.493000000000002</v>
+      </c>
+      <c r="D383" s="4">
+        <v>32.606999999999999</v>
+      </c>
+      <c r="E383">
+        <v>32.555</v>
+      </c>
+      <c r="F383" s="8">
+        <v>32.61</v>
+      </c>
+    </row>
+    <row r="384" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A384">
+        <v>383</v>
+      </c>
+      <c r="B384">
+        <v>32.793999999999997</v>
+      </c>
+      <c r="C384">
+        <v>32.502000000000002</v>
+      </c>
+      <c r="D384" s="4">
+        <v>32.613999999999997</v>
+      </c>
+      <c r="E384">
+        <v>32.552999999999997</v>
+      </c>
+      <c r="F384" s="8">
+        <v>32.61</v>
+      </c>
+    </row>
+    <row r="385" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A385">
+        <v>384</v>
+      </c>
+      <c r="B385">
+        <v>32.792999999999999</v>
+      </c>
+      <c r="C385">
+        <v>32.5</v>
+      </c>
+      <c r="D385" s="4">
+        <v>32.607999999999997</v>
+      </c>
+      <c r="E385">
+        <v>32.567999999999998</v>
+      </c>
+      <c r="F385" s="8">
+        <v>32.613999999999997</v>
+      </c>
+    </row>
+    <row r="386" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A386">
+        <v>385</v>
+      </c>
+      <c r="B386">
+        <v>32.786999999999999</v>
+      </c>
+      <c r="C386">
+        <v>32.5</v>
+      </c>
+      <c r="D386" s="4">
+        <v>32.615000000000002</v>
+      </c>
+      <c r="E386">
+        <v>32.566000000000003</v>
+      </c>
+      <c r="F386" s="8">
+        <v>32.612000000000002</v>
+      </c>
+    </row>
+    <row r="387" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A387">
+        <v>386</v>
+      </c>
+      <c r="B387">
+        <v>32.789000000000001</v>
+      </c>
+      <c r="C387">
+        <v>32.505000000000003</v>
+      </c>
+      <c r="D387" s="4">
+        <v>32.609000000000002</v>
+      </c>
+      <c r="E387">
+        <v>32.56</v>
+      </c>
+      <c r="F387" s="8">
+        <v>32.613999999999997</v>
+      </c>
+    </row>
+    <row r="388" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A388">
+        <v>387</v>
+      </c>
+      <c r="B388">
+        <v>32.774000000000001</v>
+      </c>
+      <c r="C388">
+        <v>32.503999999999998</v>
+      </c>
+      <c r="D388" s="4">
+        <v>32.603000000000002</v>
+      </c>
+      <c r="E388">
+        <v>32.566000000000003</v>
+      </c>
+      <c r="F388" s="8">
+        <v>32.610999999999997</v>
+      </c>
+    </row>
+    <row r="389" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A389">
+        <v>388</v>
+      </c>
+      <c r="B389">
+        <v>32.758000000000003</v>
+      </c>
+      <c r="C389">
+        <v>32.505000000000003</v>
+      </c>
+      <c r="D389" s="4">
+        <v>32.601999999999997</v>
+      </c>
+      <c r="E389">
+        <v>32.564</v>
+      </c>
+      <c r="F389" s="8">
+        <v>32.616</v>
+      </c>
+    </row>
+    <row r="390" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A390">
+        <v>389</v>
+      </c>
+      <c r="B390" s="1">
+        <v>32.802999999999997</v>
+      </c>
+      <c r="C390">
+        <v>32.505000000000003</v>
+      </c>
+      <c r="D390" s="4">
+        <v>32.604999999999997</v>
+      </c>
+      <c r="E390">
+        <v>32.567</v>
+      </c>
+      <c r="F390" s="8">
+        <v>32.618000000000002</v>
+      </c>
+    </row>
+    <row r="391" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A391">
+        <v>390</v>
+      </c>
+      <c r="B391">
+        <v>32.787999999999997</v>
+      </c>
+      <c r="C391">
+        <v>32.506</v>
+      </c>
+      <c r="D391" s="4">
+        <v>32.607999999999997</v>
+      </c>
+      <c r="E391">
+        <v>32.564</v>
+      </c>
+      <c r="F391" s="8">
+        <v>32.613999999999997</v>
+      </c>
+    </row>
+    <row r="392" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A392">
+        <v>391</v>
+      </c>
+      <c r="B392">
+        <v>32.777000000000001</v>
+      </c>
+      <c r="C392">
+        <v>32.5</v>
+      </c>
+      <c r="D392" s="4">
+        <v>32.606000000000002</v>
+      </c>
+      <c r="E392" s="1">
+        <v>32.572000000000003</v>
+      </c>
+      <c r="F392" s="8">
+        <v>32.615000000000002</v>
+      </c>
+    </row>
+    <row r="393" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A393">
+        <v>392</v>
+      </c>
+      <c r="B393">
+        <v>32.787999999999997</v>
+      </c>
+      <c r="C393">
+        <v>32.5</v>
+      </c>
+      <c r="D393" s="4">
+        <v>32.61</v>
+      </c>
+      <c r="E393" s="2">
+        <v>32.573</v>
+      </c>
+      <c r="F393" s="8">
+        <v>32.619</v>
+      </c>
+    </row>
+    <row r="394" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A394">
+        <v>393</v>
+      </c>
+      <c r="B394">
+        <v>32.789000000000001</v>
+      </c>
+      <c r="C394">
+        <v>32.503</v>
+      </c>
+      <c r="D394" s="4">
+        <v>32.606999999999999</v>
+      </c>
+      <c r="E394">
+        <v>32.57</v>
+      </c>
+      <c r="F394" s="8">
+        <v>32.619999999999997</v>
+      </c>
+    </row>
+    <row r="395" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A395">
+        <v>394</v>
+      </c>
+      <c r="B395">
+        <v>32.768000000000001</v>
+      </c>
+      <c r="C395">
+        <v>32.508000000000003</v>
+      </c>
+      <c r="D395" s="4">
+        <v>32.607999999999997</v>
+      </c>
+      <c r="E395">
+        <v>32.563000000000002</v>
+      </c>
+      <c r="F395" s="8">
+        <v>32.619</v>
+      </c>
+    </row>
+    <row r="396" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A396">
+        <v>395</v>
+      </c>
+      <c r="B396">
+        <v>32.78</v>
+      </c>
+      <c r="C396">
+        <v>32.505000000000003</v>
+      </c>
+      <c r="D396" s="4">
+        <v>32.607999999999997</v>
+      </c>
+      <c r="E396">
+        <v>32.566000000000003</v>
+      </c>
+      <c r="F396" s="8">
+        <v>32.618000000000002</v>
+      </c>
+    </row>
+    <row r="397" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A397">
+        <v>396</v>
+      </c>
+      <c r="B397">
+        <v>32.779000000000003</v>
+      </c>
+      <c r="C397">
+        <v>32.503999999999998</v>
+      </c>
+      <c r="D397" s="4">
+        <v>32.609000000000002</v>
+      </c>
+      <c r="E397">
+        <v>32.561</v>
+      </c>
+      <c r="F397" s="8">
+        <v>32.618000000000002</v>
+      </c>
+    </row>
+    <row r="398" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A398">
+        <v>397</v>
+      </c>
+      <c r="B398">
+        <v>32.781999999999996</v>
+      </c>
+      <c r="C398">
+        <v>32.500999999999998</v>
+      </c>
+      <c r="D398" s="4">
+        <v>32.607999999999997</v>
+      </c>
+      <c r="E398">
+        <v>32.567</v>
+      </c>
+      <c r="F398" s="8">
+        <v>32.616</v>
+      </c>
+    </row>
+    <row r="399" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A399">
+        <v>398</v>
+      </c>
+      <c r="B399">
+        <v>32.78</v>
+      </c>
+      <c r="C399">
+        <v>32.500999999999998</v>
+      </c>
+      <c r="D399" s="4">
+        <v>32.61</v>
+      </c>
+      <c r="E399">
+        <v>32.558</v>
+      </c>
+      <c r="F399" s="8">
+        <v>32.613999999999997</v>
+      </c>
+    </row>
+    <row r="400" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A400">
+        <v>399</v>
+      </c>
+      <c r="B400">
+        <v>32.789000000000001</v>
+      </c>
+      <c r="C400">
+        <v>32.499000000000002</v>
+      </c>
+      <c r="D400" s="4">
+        <v>32.613</v>
+      </c>
+      <c r="E400">
+        <v>32.561</v>
+      </c>
+      <c r="F400" s="8">
+        <v>32.616</v>
+      </c>
+    </row>
+    <row r="401" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A401">
+        <v>400</v>
+      </c>
+      <c r="B401">
+        <v>32.780999999999999</v>
+      </c>
+      <c r="C401">
+        <v>32.500999999999998</v>
+      </c>
+      <c r="D401" s="4">
+        <v>32.615000000000002</v>
+      </c>
+      <c r="E401">
+        <v>32.563000000000002</v>
+      </c>
+      <c r="F401" s="8">
+        <v>32.619999999999997</v>
+      </c>
+    </row>
+    <row r="402" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A402">
+        <v>401</v>
+      </c>
+      <c r="B402">
+        <v>32.779000000000003</v>
+      </c>
+      <c r="C402">
+        <v>32.503999999999998</v>
+      </c>
+      <c r="D402" s="4">
+        <v>32.613999999999997</v>
+      </c>
+      <c r="E402">
+        <v>32.563000000000002</v>
+      </c>
+      <c r="F402" s="8">
+        <v>32.622</v>
+      </c>
+    </row>
+    <row r="403" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A403">
+        <v>402</v>
+      </c>
+      <c r="B403">
+        <v>32.768999999999998</v>
+      </c>
+      <c r="C403">
+        <v>32.505000000000003</v>
+      </c>
+      <c r="D403" s="4">
+        <v>32.613999999999997</v>
+      </c>
+      <c r="E403">
+        <v>32.567999999999998</v>
+      </c>
+      <c r="F403" s="8">
+        <v>32.616999999999997</v>
+      </c>
+    </row>
+    <row r="404" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A404">
+        <v>403</v>
+      </c>
+      <c r="B404">
+        <v>32.787999999999997</v>
+      </c>
+      <c r="C404">
+        <v>32.505000000000003</v>
+      </c>
+      <c r="D404" s="4">
+        <v>32.613</v>
+      </c>
+      <c r="E404">
+        <v>32.564999999999998</v>
+      </c>
+      <c r="F404" s="8">
+        <v>32.619999999999997</v>
+      </c>
+    </row>
+    <row r="405" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A405">
+        <v>404</v>
+      </c>
+      <c r="B405">
+        <v>32.765999999999998</v>
+      </c>
+      <c r="C405">
+        <v>32.505000000000003</v>
+      </c>
+      <c r="D405" s="4">
+        <v>32.61</v>
+      </c>
+      <c r="E405">
+        <v>32.558999999999997</v>
+      </c>
+      <c r="F405" s="8">
+        <v>32.622</v>
+      </c>
+    </row>
+    <row r="406" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A406">
+        <v>405</v>
+      </c>
+      <c r="B406">
+        <v>32.777000000000001</v>
+      </c>
+      <c r="C406">
+        <v>32.5</v>
+      </c>
+      <c r="D406" s="4">
+        <v>32.612000000000002</v>
+      </c>
+      <c r="E406">
+        <v>32.567999999999998</v>
+      </c>
+      <c r="F406" s="8">
+        <v>32.622</v>
+      </c>
+    </row>
+    <row r="407" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A407">
+        <v>406</v>
+      </c>
+      <c r="B407" s="2">
+        <v>32.804000000000002</v>
+      </c>
+      <c r="C407">
+        <v>32.503999999999998</v>
+      </c>
+      <c r="D407" s="4">
+        <v>32.612000000000002</v>
+      </c>
+      <c r="E407">
+        <v>32.564999999999998</v>
+      </c>
+      <c r="F407" s="8">
+        <v>32.619</v>
+      </c>
+    </row>
+    <row r="408" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A408">
+        <v>407</v>
+      </c>
+      <c r="B408">
+        <v>32.777000000000001</v>
+      </c>
+      <c r="C408">
+        <v>32.503</v>
+      </c>
+      <c r="D408" s="4">
+        <v>32.612000000000002</v>
+      </c>
+      <c r="E408">
+        <v>32.567</v>
+      </c>
+      <c r="F408" s="8">
+        <v>32.616999999999997</v>
+      </c>
+    </row>
+    <row r="409" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A409">
+        <v>408</v>
+      </c>
+      <c r="B409">
+        <v>32.792000000000002</v>
+      </c>
+      <c r="C409">
+        <v>32.503</v>
+      </c>
+      <c r="D409" s="4">
+        <v>32.612000000000002</v>
+      </c>
+      <c r="E409">
+        <v>32.564999999999998</v>
+      </c>
+      <c r="F409" s="8">
+        <v>32.621000000000002</v>
+      </c>
+    </row>
+    <row r="410" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A410">
+        <v>409</v>
+      </c>
+      <c r="B410">
+        <v>32.781999999999996</v>
+      </c>
+      <c r="C410">
+        <v>32.500999999999998</v>
+      </c>
+      <c r="D410" s="4">
+        <v>32.609000000000002</v>
+      </c>
+      <c r="E410">
+        <v>32.566000000000003</v>
+      </c>
+      <c r="F410" s="8">
+        <v>32.622</v>
+      </c>
+    </row>
+    <row r="411" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A411">
+        <v>410</v>
+      </c>
+      <c r="B411">
+        <v>32.776000000000003</v>
+      </c>
+      <c r="C411">
+        <v>32.502000000000002</v>
+      </c>
+      <c r="D411" s="4">
+        <v>32.610999999999997</v>
+      </c>
+      <c r="E411">
+        <v>32.563000000000002</v>
+      </c>
+      <c r="F411" s="8">
+        <v>32.616999999999997</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
